--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -1382,6 +1382,24 @@
       </c>
       <c r="E8" s="15"/>
     </row>
+    <row r="10" ht="14.25">
+      <c r="B10">
+        <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
+        <v>0.26026650896134429</v>
+      </c>
+      <c r="C10">
+        <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
+        <v>1.2097404787973858e-003</v>
+      </c>
+      <c r="D10">
+        <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
+        <v>0.17348627638780065</v>
+      </c>
+      <c r="E10">
+        <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
+        <v>1.1644145209797989e-003</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -1289,13 +1289,13 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="C3">
-        <v>1.9e-003</v>
+        <v>2.e-003</v>
       </c>
       <c r="D3">
         <v>0.17599999999999999</v>
       </c>
       <c r="E3" s="11">
-        <v>1.5e-003</v>
+        <v>2.e-003</v>
       </c>
     </row>
     <row r="4">
@@ -1306,13 +1306,13 @@
         <v>0.25700000000000001</v>
       </c>
       <c r="C4">
-        <v>1.8e-003</v>
+        <v>2.e-003</v>
       </c>
       <c r="D4">
         <v>0.16</v>
       </c>
       <c r="E4" s="11">
-        <v>3.0999999999999999e-003</v>
+        <v>3.0000000000000001e-003</v>
       </c>
     </row>
     <row r="5">
@@ -1323,7 +1323,7 @@
         <v>0.26000000000000001</v>
       </c>
       <c r="C5">
-        <v>3.2000000000000002e-003</v>
+        <v>3.0000000000000001e-003</v>
       </c>
       <c r="D5">
         <v>0.17499999999999999</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6">
         <f>SQRT(C3^2+C4^2+C5^2)/3</f>
-        <v>1.3780017739062926e-003</v>
+        <v>1.3743685418725535e-003</v>
       </c>
       <c r="D6">
         <f>AVERAGE(D3:D5)</f>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="E6" s="11">
         <f>AVERAGE(E3:E5)</f>
-        <v>2.3e-003</v>
+        <v>2.4333333333333334e-003</v>
       </c>
     </row>
     <row r="7">
@@ -1385,19 +1385,19 @@
     <row r="10" ht="14.25">
       <c r="B10">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
-        <v>0.26026650896134429</v>
+        <v>0.26040909090909087</v>
       </c>
       <c r="C10">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
-        <v>1.2097404787973858e-003</v>
+        <v>1.2792042981336627e-003</v>
       </c>
       <c r="D10">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
-        <v>0.17348627638780065</v>
+        <v>0.17242493080080176</v>
       </c>
       <c r="E10">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
-        <v>1.1644145209797989e-003</v>
+        <v>1.3482195315735518e-003</v>
       </c>
     </row>
   </sheetData>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -69,97 +69,97 @@
     <t xml:space="preserve">sm (kg)</t>
   </si>
   <si>
+    <t>x_best</t>
+  </si>
+  <si>
+    <t>sx_best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpolazione piano inclinato</t>
+  </si>
+  <si>
+    <t>Angolo</t>
+  </si>
+  <si>
+    <t>incertezza</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
+    <t>θ</t>
+  </si>
+  <si>
+    <t>sθ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area (N*s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (N*s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velocità iniziale (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velocità finale (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impulso (N*s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔE (J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coeff. di restituzione</t>
+  </si>
+  <si>
+    <t>Magnete</t>
+  </si>
+  <si>
+    <t>Molla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrello rosso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrello blu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantità di moto iniziale (kg*m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantità di moto finale (kg*m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energia inizale (J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energia finale (J)</t>
+  </si>
+  <si>
+    <t>Velcro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 libro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 libri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F (N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coefficiente angolare</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Incertezza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Errore sulla media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpolazione piano inclinato</t>
-  </si>
-  <si>
-    <t>Angolo</t>
-  </si>
-  <si>
-    <t>incertezza</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>sm</t>
-  </si>
-  <si>
-    <t>θ</t>
-  </si>
-  <si>
-    <t>sθ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area (N*s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (N*s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velocità iniziale (m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velocità finale (m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impulso (N*s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔE (J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coeff. di restituzione</t>
-  </si>
-  <si>
-    <t>Magnete</t>
-  </si>
-  <si>
-    <t>Molla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrello rosso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrello blu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantità di moto iniziale (kg*m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantità di moto finale (kg*m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energia inizale (J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energia finale (J)</t>
-  </si>
-  <si>
-    <t>Velcro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 libro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 libri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F (N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coefficiente angolare</t>
   </si>
   <si>
     <t xml:space="preserve">Errore della media</t>
@@ -169,9 +169,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -219,7 +220,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="32">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -315,11 +316,239 @@
     </border>
     <border>
       <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -348,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="85">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -366,31 +595,81 @@
     <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="24" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -403,24 +682,26 @@
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="5" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="5" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -429,7 +710,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1081,8 +1362,10 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="11.73046875"/>
-    <col customWidth="1" min="5" max="5" width="13.46484375"/>
+    <col customWidth="1" min="2" max="2" width="11.50390625"/>
+    <col customWidth="1" min="3" max="3" width="12.00390625"/>
+    <col customWidth="1" min="4" max="4" width="12.75390625"/>
+    <col customWidth="1" min="5" max="5" width="13.50390625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1094,141 +1377,113 @@
       <c r="D1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="18"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16">
+      <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="27">
         <v>0.249</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="28">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="29">
         <v>0.76900000000000002</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="30">
         <v>4.2999999999999997e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="32">
         <v>0.253</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="33">
         <v>4.2999999999999997e-002</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="34">
         <v>0.755</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="35">
         <v>3.7999999999999999e-002</v>
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="24">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="32">
         <v>0.247</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="36">
         <v>4.2000000000000003e-002</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="34">
         <v>0.749</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="35">
         <v>3.7999999999999999e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="20">
-        <f>AVERAGE(B3:B5)</f>
-        <v>0.24966666666666668</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6">
-        <f>AVERAGE(D3:D5)</f>
-        <v>0.75766666666666671</v>
-      </c>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="20">
-        <f>_xlfn.STDEV.S(B3:B5)</f>
-        <v>3.0550504633038958e-003</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7">
-        <f>_xlfn.STDEV.S(D3:D5)</f>
-        <v>1.0263202878893778e-002</v>
-      </c>
-      <c r="E7" s="11"/>
-    </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="24">
-        <f>B7/SQRT(3)</f>
-        <v>1.7638342073763953e-003</v>
-      </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="13">
-        <f>D7/SQRT(3)</f>
-        <v>5.9254629448770649e-003</v>
-      </c>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="B10">
+      <c r="B6" s="38">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.24959417617111146</v>
       </c>
-      <c r="C10">
+      <c r="C6" s="39"/>
+      <c r="D6" s="40">
+        <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
+        <v>0.75677401789187093</v>
+      </c>
+      <c r="E6" s="41"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="43">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
         <v>2.4023430034058289e-002</v>
       </c>
-      <c r="D10">
-        <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
-        <v>0.75677401789187093</v>
-      </c>
-      <c r="E10">
+      <c r="C7" s="44"/>
+      <c r="D7" s="45">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
         <v>2.2786940380104245e-002</v>
       </c>
-    </row>
+      <c r="E7" s="46"/>
+    </row>
+    <row r="8" ht="14.65"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1247,45 +1502,45 @@
   <sheetData>
     <row r="1" ht="14.65">
       <c r="A1" s="16"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="27" t="s">
+      <c r="G1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="6" t="s">
+    </row>
+    <row r="2" ht="14.65">
+      <c r="A2" s="21"/>
+      <c r="B2" s="51" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="A2" s="20"/>
-      <c r="B2" s="28" t="s">
+      <c r="C2" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="D2" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="F2" s="54">
         <v>10</v>
       </c>
-      <c r="G2" s="31">
+      <c r="G2" s="55">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20">
+      <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3">
         <v>0.26400000000000001</v>
       </c>
       <c r="C3">
@@ -1299,16 +1554,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4">
         <v>0.25700000000000001</v>
       </c>
       <c r="C4">
         <v>2.e-003</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="56">
         <v>0.16</v>
       </c>
       <c r="E4" s="11">
@@ -1316,10 +1571,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5">
         <v>0.26000000000000001</v>
       </c>
       <c r="C5">
@@ -1333,76 +1588,43 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="20">
-        <f>AVERAGE(B3:B5)</f>
-        <v>0.26033333333333336</v>
-      </c>
-      <c r="C6">
-        <f>SQRT(C3^2+C4^2+C5^2)/3</f>
-        <v>1.3743685418725535e-003</v>
-      </c>
-      <c r="D6">
-        <f>AVERAGE(D3:D5)</f>
-        <v>0.17033333333333331</v>
-      </c>
-      <c r="E6" s="11">
-        <f>AVERAGE(E3:E5)</f>
-        <v>2.4333333333333334e-003</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="20">
-        <f>_xlfn.STDEV.S(B3:B5)</f>
-        <v>3.5118845842842493e-003</v>
-      </c>
-      <c r="D7">
-        <f>_xlfn.STDEV.S(D3:D5)</f>
-        <v>8.9628864398324931e-003</v>
-      </c>
-      <c r="E7" s="11"/>
-    </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="24">
-        <f>B7/SQRT(3)</f>
-        <v>2.0275875100994084e-003</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13">
-        <f>D7/SQRT(3)</f>
-        <v>5.1747248987533368e-003</v>
-      </c>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="B10">
+      <c r="B6" s="38">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.26040909090909087</v>
       </c>
-      <c r="C10">
+      <c r="C6" s="39"/>
+      <c r="D6" s="40">
+        <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
+        <v>0.17242493080080176</v>
+      </c>
+      <c r="E6" s="41"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="38">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
         <v>1.2792042981336627e-003</v>
       </c>
-      <c r="D10">
-        <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
-        <v>0.17242493080080176</v>
-      </c>
-      <c r="E10">
+      <c r="C7" s="39"/>
+      <c r="D7" s="40">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
         <v>1.3482195315735518e-003</v>
       </c>
-    </row>
+      <c r="E7" s="41"/>
+    </row>
+    <row r="8" ht="14.65"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1429,36 +1651,36 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="E1" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F1" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="G1" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="H1" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="23" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="57" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="32">
+      <c r="B2" s="58">
         <v>0.27538000000000001</v>
       </c>
       <c r="C2" s="1">
@@ -1474,7 +1696,7 @@
       <c r="F2" s="1">
         <v>-0.54000000000000004</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="59">
         <f>0.27538*(F2-E2)</f>
         <v>-0.30291800000000002</v>
       </c>
@@ -1482,16 +1704,16 @@
         <f t="shared" ref="H2:H3" si="0">0.5*B2*(F2-E2)^2</f>
         <v>0.16660490000000003</v>
       </c>
-      <c r="I2" s="34">
+      <c r="I2" s="60">
         <f t="shared" ref="I2:I3" si="1">-(B2*F2)/(B2*E2)</f>
         <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="35">
+      <c r="A3" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="61">
         <v>0.25686999999999999</v>
       </c>
       <c r="C3" s="13">
@@ -1544,54 +1766,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="63"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="39" t="s">
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+    </row>
+    <row r="2" ht="14.65">
+      <c r="B2" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-    </row>
-    <row r="2" ht="14.65">
-      <c r="B2" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="41" t="s">
+      <c r="I2" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="J2" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="41" t="s">
+      <c r="K2" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="42" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="32">
+      <c r="A3" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="58">
         <v>0.25634000000000001</v>
       </c>
       <c r="C3" s="1">
@@ -1600,7 +1822,7 @@
       <c r="D3" s="1">
         <v>-2.e-003</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="58">
         <v>0.27538000000000001</v>
       </c>
       <c r="F3" s="1">
@@ -1613,7 +1835,7 @@
         <f t="shared" ref="H3:H8" si="2">B3*C3</f>
         <v>0.13714190000000001</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="60">
         <f t="shared" ref="I3:I8" si="3">B3*D3+E3*G3</f>
         <v>0.12561136000000003</v>
       </c>
@@ -1621,23 +1843,23 @@
         <f t="shared" ref="J3:J8" si="4">0.5*B3*C3^2</f>
         <v>3.6685458250000004e-002</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="60">
         <f t="shared" ref="K3:K8" si="5">0.5*(B3*D3^2+E3*G3^2)</f>
         <v>2.8882917840000001e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44"/>
-      <c r="B4" s="45">
+      <c r="A4" s="72"/>
+      <c r="B4" s="73">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="56">
         <v>0.53000000000000003</v>
       </c>
       <c r="D4">
         <v>-0.22600000000000001</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="73">
         <v>0.78227999999999998</v>
       </c>
       <c r="F4">
@@ -1646,7 +1868,7 @@
       <c r="G4">
         <v>0.24299999999999999</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="21">
         <f t="shared" si="2"/>
         <v>0.13586020000000001</v>
       </c>
@@ -1654,7 +1876,7 @@
         <f t="shared" si="3"/>
         <v>0.13216119999999998</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="21">
         <f t="shared" si="4"/>
         <v>3.6002953000000004e-002</v>
       </c>
@@ -1664,8 +1886,8 @@
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="47"/>
-      <c r="B5" s="24">
+      <c r="A5" s="74"/>
+      <c r="B5" s="75">
         <v>0.76324000000000003</v>
       </c>
       <c r="C5" s="13">
@@ -1674,7 +1896,7 @@
       <c r="D5" s="13">
         <v>0.158</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="61">
         <v>0.27538000000000001</v>
       </c>
       <c r="F5" s="13">
@@ -1683,7 +1905,7 @@
       <c r="G5" s="13">
         <v>0.48499999999999999</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="75">
         <f t="shared" si="2"/>
         <v>0.28087232000000001</v>
       </c>
@@ -1691,7 +1913,7 @@
         <f t="shared" si="3"/>
         <v>0.25415122000000001</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="75">
         <f t="shared" si="4"/>
         <v>5.1680506879999998e-002</v>
       </c>
@@ -1701,16 +1923,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="32">
+      <c r="A6" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="58">
         <v>0.25634000000000001</v>
       </c>
       <c r="C6" s="1">
         <v>0.57799999999999996</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="60">
         <v>0.253</v>
       </c>
       <c r="E6" s="1">
@@ -1722,7 +1944,7 @@
       <c r="G6" s="1">
         <v>0.253</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f t="shared" si="2"/>
         <v>0.14816451999999999</v>
       </c>
@@ -1730,7 +1952,7 @@
         <f t="shared" si="3"/>
         <v>0.13452516</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="21">
         <f t="shared" si="4"/>
         <v>4.2819546279999995e-002</v>
       </c>
@@ -1740,8 +1962,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49"/>
-      <c r="B7" s="45">
+      <c r="A7" s="77"/>
+      <c r="B7" s="73">
         <v>0.25634000000000001</v>
       </c>
       <c r="C7">
@@ -1750,7 +1972,7 @@
       <c r="D7" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="73">
         <v>0.78227999999999998</v>
       </c>
       <c r="F7">
@@ -1759,7 +1981,7 @@
       <c r="G7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="21">
         <f t="shared" si="2"/>
         <v>0.14662648</v>
       </c>
@@ -1767,7 +1989,7 @@
         <f t="shared" si="3"/>
         <v>0.1454068</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="21">
         <f t="shared" si="4"/>
         <v>4.1935173279999995e-002</v>
       </c>
@@ -1777,8 +1999,8 @@
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="50"/>
-      <c r="B8" s="24">
+      <c r="A8" s="78"/>
+      <c r="B8" s="75">
         <v>0.76324000000000003</v>
       </c>
       <c r="C8" s="13">
@@ -1787,7 +2009,7 @@
       <c r="D8" s="15">
         <v>0.34399999999999997</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="61">
         <v>0.27538000000000001</v>
       </c>
       <c r="F8" s="13">
@@ -1796,7 +2018,7 @@
       <c r="G8" s="13">
         <v>0.34399999999999997</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="75">
         <f t="shared" si="2"/>
         <v>0.36482872</v>
       </c>
@@ -1804,7 +2026,7 @@
         <f t="shared" si="3"/>
         <v>0.35728527999999998</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="75">
         <f t="shared" si="4"/>
         <v>8.7194064079999994e-002</v>
       </c>
@@ -1814,7 +2036,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51"/>
+      <c r="A9" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1835,31 +2057,31 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="49"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="18"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>44</v>
+      <c r="C2" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="24">
+      <c r="A3" s="75">
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="15">
@@ -1899,48 +2121,48 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="80">
+        <v>1.478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="80">
+        <v>1.5192000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="80">
+        <v>1.5113000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="80">
+        <v>1.5176000000000001</v>
+      </c>
+    </row>
+    <row r="6" ht="14.65">
+      <c r="B6" s="80">
+        <v>1.5246999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="52">
-        <v>1.478</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="52">
-        <v>1.5192000000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="52">
-        <v>1.5113000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="52">
-        <v>1.5176000000000001</v>
-      </c>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="B6" s="52">
-        <v>1.5246999999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="54">
+      <c r="B7" s="82">
         <f>AVERAGE(B2:B6)</f>
         <v>1.5101600000000002</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="84">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>
         <v>8.3188100110532705e-003</v>
       </c>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -182,7 +182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,7 +201,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="5"/>
+        <fgColor rgb="FF4285F4"/>
+        <bgColor rgb="FF4285F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFC00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,16 +229,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor indexed="5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="37">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -235,6 +248,322 @@
         <color auto="1"/>
       </top>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -246,6 +575,35 @@
         <color auto="1"/>
       </top>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -262,7 +620,9 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="none"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -283,351 +643,61 @@
       </bottom>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color theme="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="97">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="10" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="24" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="26" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="27" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -636,85 +706,103 @@
     <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="7" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="7" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="7" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="33" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="8" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="9" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="9" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1238,13 +1326,13 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.19921875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.9296875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="13.3984375"/>
-    <col bestFit="1" customWidth="1" min="4" max="5" width="10.796875"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14.265625"/>
-    <col bestFit="1" customWidth="1" min="7" max="8" width="15.1328125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="18.3984375"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="16.875"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="15.453125"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="13.953125"/>
+    <col bestFit="1" customWidth="1" min="4" max="5" width="11.54296875"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="14.953125"/>
+    <col bestFit="1" customWidth="1" min="7" max="8" width="16.04296875"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="19.29296875"/>
     <col bestFit="1" customWidth="1" min="10" max="10" width="11.46484375"/>
     <col bestFit="1" customWidth="1" min="11" max="12" width="18.3984375"/>
     <col bestFit="1" customWidth="1" min="13" max="13" width="13.1328125"/>
@@ -1265,86 +1353,90 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9">
         <v>0.25452000000000002</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="9">
         <v>0.25314999999999999</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="9">
         <v>0.25374999999999998</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <f>SUM(C2:E2)</f>
         <v>0.76141999999999999</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="9">
         <v>0.29006999999999999</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>0.18593999999999999</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>5.0000000000000001e-004</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="13">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="14">
         <v>0.27538000000000001</v>
       </c>
-      <c r="F3" s="8">
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3" s="14">
         <f>C3+D2+E2</f>
         <v>0.78227999999999986</v>
       </c>
-      <c r="H3" s="11"/>
+      <c r="G3"/>
+      <c r="H3" s="15"/>
     </row>
     <row r="4" ht="14.65">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14">
+      <c r="B4" s="17"/>
+      <c r="C4" s="18">
         <v>0.25686999999999999</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="8">
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="18">
         <f>B3+D2+E2</f>
         <v>0.76323999999999992</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="15"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="15">
-      <c r="O15" s="8"/>
+      <c r="O15" s="14"/>
     </row>
     <row r="16">
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1369,111 +1461,111 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16"/>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="19" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="20"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="21"/>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="30" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="8">
         <v>0.249</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="32">
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="33">
         <v>0.76900000000000002</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="34">
         <v>4.2999999999999997e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31">
+      <c r="A4" s="35">
         <v>2</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="36">
         <v>0.253</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="37">
         <v>4.2999999999999997e-002</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="38">
         <v>0.755</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="15">
         <v>3.7999999999999999e-002</v>
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="31">
+      <c r="A5" s="35">
         <v>3</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>0.247</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="39">
         <v>4.2000000000000003e-002</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="38">
         <v>0.749</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="15">
         <v>3.7999999999999999e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="41">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.24959417617111146</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40">
+      <c r="C6" s="42"/>
+      <c r="D6" s="43">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.75677401789187093</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="44"/>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="46">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
         <v>2.4023430034058289e-002</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45">
+      <c r="C7" s="47"/>
+      <c r="D7" s="48">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
         <v>2.2786940380104245e-002</v>
       </c>
-      <c r="E7" s="46"/>
+      <c r="E7" s="49"/>
     </row>
     <row r="8" ht="14.65"/>
   </sheetData>
@@ -1501,43 +1593,43 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="A1" s="16"/>
-      <c r="B1" s="47" t="s">
+      <c r="A1" s="21"/>
+      <c r="B1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="50" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="21"/>
-      <c r="B2" s="51" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="58">
         <v>10</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="59">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3">
@@ -1549,12 +1641,12 @@
       <c r="D3">
         <v>0.17599999999999999</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="60">
         <v>2.e-003</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31">
+      <c r="A4" s="35">
         <v>2</v>
       </c>
       <c r="B4">
@@ -1563,15 +1655,15 @@
       <c r="C4">
         <v>2.e-003</v>
       </c>
-      <c r="D4" s="56">
+      <c r="D4" s="61">
         <v>0.16</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="60">
         <v>3.0000000000000001e-003</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31">
+      <c r="A5" s="35">
         <v>3</v>
       </c>
       <c r="B5">
@@ -1583,39 +1675,39 @@
       <c r="D5">
         <v>0.17499999999999999</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="60">
         <v>2.3e-003</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="41">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.26040909090909087</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40">
+      <c r="C6" s="42"/>
+      <c r="D6" s="43">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.17242493080080176</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="44"/>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="41">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
         <v>1.2792042981336627e-003</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40">
+      <c r="C7" s="42"/>
+      <c r="D7" s="43">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
         <v>1.3482195315735518e-003</v>
       </c>
-      <c r="E7" s="41"/>
+      <c r="E7" s="44"/>
     </row>
     <row r="8" ht="14.65"/>
   </sheetData>
@@ -1651,36 +1743,36 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="57" t="s">
+      <c r="G1" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="62" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="63">
         <v>0.27538000000000001</v>
       </c>
       <c r="C2" s="1">
@@ -1696,7 +1788,7 @@
       <c r="F2" s="1">
         <v>-0.54000000000000004</v>
       </c>
-      <c r="G2" s="59">
+      <c r="G2" s="64">
         <f>0.27538*(F2-E2)</f>
         <v>-0.30291800000000002</v>
       </c>
@@ -1704,40 +1796,40 @@
         <f t="shared" ref="H2:H3" si="0">0.5*B2*(F2-E2)^2</f>
         <v>0.16660490000000003</v>
       </c>
-      <c r="I2" s="60">
+      <c r="I2" s="65">
         <f t="shared" ref="I2:I3" si="1">-(B2*F2)/(B2*E2)</f>
         <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="66">
         <v>0.25686999999999999</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="67">
         <v>-0.28999999999999998</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="67">
         <f>0.07/SQRT(3)</f>
         <v>4.0414518843273808e-002</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="67">
         <v>0.64000000000000001</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="67">
         <v>-0.62</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="68">
         <f>0.25687*(F3-E3)</f>
         <v>-0.32365620000000001</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="67">
         <f t="shared" si="0"/>
         <v>0.20390340600000001</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="69">
         <f t="shared" si="1"/>
         <v>0.96875000000000011</v>
       </c>
@@ -1766,54 +1858,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65" t="s">
+      <c r="C1" s="71"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="2" ht="14.65">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="69" t="s">
+      <c r="H2" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="69" t="s">
+      <c r="J2" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="70" t="s">
+      <c r="K2" s="78" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="63">
         <v>0.25634000000000001</v>
       </c>
       <c r="C3" s="1">
@@ -1822,7 +1914,7 @@
       <c r="D3" s="1">
         <v>-2.e-003</v>
       </c>
-      <c r="E3" s="58">
+      <c r="E3" s="63">
         <v>0.27538000000000001</v>
       </c>
       <c r="F3" s="1">
@@ -1831,35 +1923,35 @@
       <c r="G3" s="1">
         <v>0.45800000000000002</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H8" si="2">B3*C3</f>
         <v>0.13714190000000001</v>
       </c>
-      <c r="I3" s="60">
+      <c r="I3" s="65">
         <f t="shared" ref="I3:I8" si="3">B3*D3+E3*G3</f>
         <v>0.12561136000000003</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="21">
         <f t="shared" ref="J3:J8" si="4">0.5*B3*C3^2</f>
         <v>3.6685458250000004e-002</v>
       </c>
-      <c r="K3" s="60">
+      <c r="K3" s="65">
         <f t="shared" ref="K3:K8" si="5">0.5*(B3*D3^2+E3*G3^2)</f>
         <v>2.8882917840000001e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72"/>
-      <c r="B4" s="73">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="61">
         <v>0.53000000000000003</v>
       </c>
       <c r="D4">
         <v>-0.22600000000000001</v>
       </c>
-      <c r="E4" s="73">
+      <c r="E4" s="81">
         <v>0.78227999999999998</v>
       </c>
       <c r="F4">
@@ -1868,71 +1960,71 @@
       <c r="G4">
         <v>0.24299999999999999</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="26">
         <f t="shared" si="2"/>
         <v>0.13586020000000001</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="60">
         <f t="shared" si="3"/>
         <v>0.13216119999999998</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="26">
         <f t="shared" si="4"/>
         <v>3.6002953000000004e-002</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="60">
         <f t="shared" si="5"/>
         <v>2.9642836780000001e-002</v>
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="74"/>
-      <c r="B5" s="75">
+      <c r="A5" s="82"/>
+      <c r="B5" s="83">
         <v>0.76324000000000003</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="67">
         <v>0.36799999999999999</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="67">
         <v>0.158</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="66">
         <v>0.27538000000000001</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="67">
         <v>0</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="67">
         <v>0.48499999999999999</v>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="83">
         <f t="shared" si="2"/>
         <v>0.28087232000000001</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="69">
         <f t="shared" si="3"/>
         <v>0.25415122000000001</v>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="83">
         <f t="shared" si="4"/>
         <v>5.1680506879999998e-002</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="69">
         <f t="shared" si="5"/>
         <v>4.1914891930000003e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="63">
         <v>0.25634000000000001</v>
       </c>
       <c r="C6" s="1">
         <v>0.57799999999999996</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="65">
         <v>0.253</v>
       </c>
       <c r="E6" s="1">
@@ -1944,35 +2036,35 @@
       <c r="G6" s="1">
         <v>0.253</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="26">
         <f t="shared" si="2"/>
         <v>0.14816451999999999</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="60">
         <f t="shared" si="3"/>
         <v>0.13452516</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="26">
         <f t="shared" si="4"/>
         <v>4.2819546279999995e-002</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="60">
         <f t="shared" si="5"/>
         <v>1.7017432739999998e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="77"/>
-      <c r="B7" s="73">
+      <c r="A7" s="85"/>
+      <c r="B7" s="81">
         <v>0.25634000000000001</v>
       </c>
       <c r="C7">
         <v>0.57199999999999995</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="60">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E7" s="73">
+      <c r="E7" s="81">
         <v>0.78227999999999998</v>
       </c>
       <c r="F7">
@@ -1981,62 +2073,62 @@
       <c r="G7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="26">
         <f t="shared" si="2"/>
         <v>0.14662648</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="60">
         <f t="shared" si="3"/>
         <v>0.1454068</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="26">
         <f t="shared" si="4"/>
         <v>4.1935173279999995e-002</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="60">
         <f t="shared" si="5"/>
         <v>1.0178476000000002e-002</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="78"/>
-      <c r="B8" s="75">
+      <c r="A8" s="86"/>
+      <c r="B8" s="83">
         <v>0.76324000000000003</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="67">
         <v>0.47799999999999998</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="69">
         <v>0.34399999999999997</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="66">
         <v>0.27538000000000001</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="67">
         <v>0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="67">
         <v>0.34399999999999997</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="83">
         <f t="shared" si="2"/>
         <v>0.36482872</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="69">
         <f t="shared" si="3"/>
         <v>0.35728527999999998</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="83">
         <f t="shared" si="4"/>
         <v>8.7194064079999994e-002</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="69">
         <f t="shared" si="5"/>
         <v>6.1453068159999999e-002</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="79"/>
+      <c r="A9" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2057,41 +2149,41 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="48" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="49"/>
+      <c r="D1" s="89"/>
     </row>
     <row r="2">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="75" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="75">
+      <c r="A3" s="83">
         <v>0.29006999999999999</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="69">
         <v>0.68000000000000005</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="67">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="69">
         <v>0.93999999999999995</v>
       </c>
     </row>
@@ -2120,49 +2212,49 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="91" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="80">
+      <c r="B2" s="92">
         <v>1.478</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="80">
+      <c r="B3" s="92">
         <v>1.5192000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="80">
+      <c r="B4" s="92">
         <v>1.5113000000000001</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="80">
+      <c r="B5" s="92">
         <v>1.5176000000000001</v>
       </c>
     </row>
     <row r="6" ht="14.65">
-      <c r="B6" s="80">
+      <c r="B6" s="92">
         <v>1.5246999999999999</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="82">
+      <c r="B7" s="94">
         <f>AVERAGE(B2:B6)</f>
         <v>1.5101600000000002</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="84">
+      <c r="B8" s="96">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>
         <v>8.3188100110532705e-003</v>
       </c>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -1404,13 +1404,10 @@
       <c r="C3" s="14">
         <v>0.27538000000000001</v>
       </c>
-      <c r="D3"/>
-      <c r="E3"/>
       <c r="F3" s="14">
         <f>C3+D2+E2</f>
         <v>0.78227999999999986</v>
       </c>
-      <c r="G3"/>
       <c r="H3" s="15"/>
     </row>
     <row r="4" ht="14.65">
@@ -2177,14 +2174,14 @@
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="69">
-        <v>0.68000000000000005</v>
+        <v>0.68124660000000004</v>
       </c>
       <c r="C3" s="67">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
       <c r="D3" s="69">
-        <v>0.93999999999999995</v>
+        <v>0.93591829999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -2174,14 +2174,14 @@
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="69">
-        <v>0.68124660000000004</v>
+        <v>0.68125000000000002</v>
       </c>
       <c r="C3" s="67">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
       <c r="D3" s="69">
-        <v>0.93591829999999998</v>
+        <v>0.90805999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -2174,14 +2174,14 @@
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="69">
-        <v>0.68125000000000002</v>
+        <v>0.68120000000000003</v>
       </c>
       <c r="C3" s="67">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
       <c r="D3" s="69">
-        <v>0.90805999999999998</v>
+        <v>0.93589999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -1906,10 +1906,10 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C3" s="1">
-        <v>0.53500000000000003</v>
+        <v>0.501</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.e-003</v>
+        <v>-5.0000000000000001e-003</v>
       </c>
       <c r="E3" s="63">
         <v>0.27538000000000001</v>
@@ -1918,23 +1918,23 @@
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0.45800000000000002</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="H3" s="21">
         <f t="shared" ref="H3:H8" si="2">B3*C3</f>
-        <v>0.13714190000000001</v>
+        <v>0.12842634</v>
       </c>
       <c r="I3" s="65">
         <f t="shared" ref="I3:I8" si="3">B3*D3+E3*G3</f>
-        <v>0.12561136000000003</v>
+        <v>0.1322776</v>
       </c>
       <c r="J3" s="21">
         <f t="shared" ref="J3:J8" si="4">0.5*B3*C3^2</f>
-        <v>3.6685458250000004e-002</v>
+        <v>3.2170798170000001e-002</v>
       </c>
       <c r="K3" s="65">
         <f t="shared" ref="K3:K8" si="5">0.5*(B3*D3^2+E3*G3^2)</f>
-        <v>2.8882917840000001e-002</v>
+        <v>3.2391334500000001e-002</v>
       </c>
     </row>
     <row r="4">
@@ -1943,10 +1943,10 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C4" s="61">
-        <v>0.53000000000000003</v>
+        <v>0.497</v>
       </c>
       <c r="D4">
-        <v>-0.22600000000000001</v>
+        <v>-0.22900000000000001</v>
       </c>
       <c r="E4" s="81">
         <v>0.78227999999999998</v>
@@ -1959,19 +1959,19 @@
       </c>
       <c r="H4" s="26">
         <f t="shared" si="2"/>
-        <v>0.13586020000000001</v>
+        <v>0.12740098</v>
       </c>
       <c r="I4" s="60">
         <f t="shared" si="3"/>
-        <v>0.13216119999999998</v>
+        <v>0.13139217999999997</v>
       </c>
       <c r="J4" s="26">
         <f t="shared" si="4"/>
-        <v>3.6002953000000004e-002</v>
+        <v>3.1659143530000003e-002</v>
       </c>
       <c r="K4" s="60">
         <f t="shared" si="5"/>
-        <v>2.9642836780000001e-002</v>
+        <v>2.9817788829999997e-002</v>
       </c>
     </row>
     <row r="5" ht="14.65">
@@ -1980,10 +1980,10 @@
         <v>0.76324000000000003</v>
       </c>
       <c r="C5" s="67">
-        <v>0.36799999999999999</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="D5" s="67">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="E5" s="66">
         <v>0.27538000000000001</v>
@@ -1996,19 +1996,19 @@
       </c>
       <c r="H5" s="83">
         <f t="shared" si="2"/>
-        <v>0.28087232000000001</v>
+        <v>0.26637075999999998</v>
       </c>
       <c r="I5" s="69">
         <f t="shared" si="3"/>
-        <v>0.25415122000000001</v>
+        <v>0.25491446000000001</v>
       </c>
       <c r="J5" s="83">
         <f t="shared" si="4"/>
-        <v>5.1680506879999998e-002</v>
+        <v>4.6481697619999991e-002</v>
       </c>
       <c r="K5" s="69">
         <f t="shared" si="5"/>
-        <v>4.1914891930000003e-002</v>
+        <v>4.2035865470000003e-002</v>
       </c>
     </row>
     <row r="6">
@@ -2019,7 +2019,7 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C6" s="1">
-        <v>0.57799999999999996</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="D6" s="65">
         <v>0.253</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="H6" s="26">
         <f t="shared" si="2"/>
-        <v>0.14816451999999999</v>
+        <v>0.11996712000000001</v>
       </c>
       <c r="I6" s="60">
         <f t="shared" si="3"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="J6" s="26">
         <f t="shared" si="4"/>
-        <v>4.2819546279999995e-002</v>
+        <v>2.8072306080000005e-002</v>
       </c>
       <c r="K6" s="60">
         <f t="shared" si="5"/>
@@ -2056,7 +2056,7 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C7">
-        <v>0.57199999999999995</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="D7" s="60">
         <v>0.14000000000000001</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H7" s="26">
         <f t="shared" si="2"/>
-        <v>0.14662648</v>
+        <v>0.14431942</v>
       </c>
       <c r="I7" s="60">
         <f t="shared" si="3"/>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="J7" s="26">
         <f t="shared" si="4"/>
-        <v>4.1935173279999995e-002</v>
+        <v>4.0625916729999996e-002</v>
       </c>
       <c r="K7" s="60">
         <f t="shared" si="5"/>
@@ -2093,7 +2093,7 @@
         <v>0.76324000000000003</v>
       </c>
       <c r="C8" s="67">
-        <v>0.47799999999999998</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="D8" s="69">
         <v>0.34399999999999997</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H8" s="83">
         <f t="shared" si="2"/>
-        <v>0.36482872</v>
+        <v>0.32437700000000003</v>
       </c>
       <c r="I8" s="69">
         <f t="shared" si="3"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J8" s="83">
         <f t="shared" si="4"/>
-        <v>8.7194064079999994e-002</v>
+        <v>6.8930112500000001e-002</v>
       </c>
       <c r="K8" s="69">
         <f t="shared" si="5"/>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -1909,7 +1909,7 @@
         <v>0.501</v>
       </c>
       <c r="D3" s="1">
-        <v>-5.0000000000000001e-003</v>
+        <v>-1.6e-002</v>
       </c>
       <c r="E3" s="63">
         <v>0.27538000000000001</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="I3" s="65">
         <f t="shared" ref="I3:I8" si="3">B3*D3+E3*G3</f>
-        <v>0.1322776</v>
+        <v>0.12945785999999998</v>
       </c>
       <c r="J3" s="21">
         <f t="shared" ref="J3:J8" si="4">0.5*B3*C3^2</f>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K3" s="65">
         <f t="shared" ref="K3:K8" si="5">0.5*(B3*D3^2+E3*G3^2)</f>
-        <v>3.2391334500000001e-002</v>
+        <v>3.2420941770000003e-002</v>
       </c>
     </row>
     <row r="4">
@@ -1943,7 +1943,7 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C4" s="61">
-        <v>0.497</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="D4">
         <v>-0.22900000000000001</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="H4" s="26">
         <f t="shared" si="2"/>
-        <v>0.12740098</v>
+        <v>0.13637288</v>
       </c>
       <c r="I4" s="60">
         <f t="shared" si="3"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="J4" s="26">
         <f t="shared" si="4"/>
-        <v>3.1659143530000003e-002</v>
+        <v>3.6275186080000008e-002</v>
       </c>
       <c r="K4" s="60">
         <f t="shared" si="5"/>
@@ -1983,7 +1983,7 @@
         <v>0.34899999999999998</v>
       </c>
       <c r="D5" s="67">
-        <v>0.159</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="E5" s="66">
         <v>0.27538000000000001</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I5" s="69">
         <f t="shared" si="3"/>
-        <v>0.25491446000000001</v>
+        <v>0.26025714</v>
       </c>
       <c r="J5" s="83">
         <f t="shared" si="4"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="K5" s="69">
         <f t="shared" si="5"/>
-        <v>4.2035865470000003e-002</v>
+        <v>4.2904050970000003e-002</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -1943,7 +1943,7 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C4" s="61">
-        <v>0.53200000000000003</v>
+        <v>0.52000000000000002</v>
       </c>
       <c r="D4">
         <v>-0.22900000000000001</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="H4" s="26">
         <f t="shared" si="2"/>
-        <v>0.13637288</v>
+        <v>0.13329680000000002</v>
       </c>
       <c r="I4" s="60">
         <f t="shared" si="3"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="J4" s="26">
         <f t="shared" si="4"/>
-        <v>3.6275186080000008e-002</v>
+        <v>3.4657168000000002e-002</v>
       </c>
       <c r="K4" s="60">
         <f t="shared" si="5"/>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -1943,7 +1943,7 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C4" s="61">
-        <v>0.52000000000000002</v>
+        <v>0.497</v>
       </c>
       <c r="D4">
         <v>-0.22900000000000001</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="H4" s="26">
         <f t="shared" si="2"/>
-        <v>0.13329680000000002</v>
+        <v>0.12740098</v>
       </c>
       <c r="I4" s="60">
         <f t="shared" si="3"/>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="J4" s="26">
         <f t="shared" si="4"/>
-        <v>3.4657168000000002e-002</v>
+        <v>3.1659143530000003e-002</v>
       </c>
       <c r="K4" s="60">
         <f t="shared" si="5"/>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">Carrello rosso (kg)</t>
   </si>
@@ -132,6 +132,9 @@
     <t xml:space="preserve">Carrello blu</t>
   </si>
   <si>
+    <t xml:space="preserve">sv (m/s)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantità di moto iniziale (kg*m/s)</t>
   </si>
   <si>
@@ -142,6 +145,9 @@
   </si>
   <si>
     <t xml:space="preserve">Energia finale (J)</t>
+  </si>
+  <si>
+    <t>0.008</t>
   </si>
   <si>
     <t>Velcro</t>
@@ -182,7 +188,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,11 +235,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -605,6 +617,15 @@
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -748,13 +769,10 @@
     <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="31" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -762,47 +780,42 @@
     </xf>
     <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="31" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="33" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="10" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="10" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="9" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="10" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="35" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="35" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="34" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="36" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="37" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1843,13 +1856,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="9"/>
-    <col bestFit="1" customWidth="1" min="3" max="4" width="16.33203125"/>
+    <col customWidth="1" min="2" max="2" width="14.00390625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="17.79296875"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="16.54296875"/>
     <col bestFit="1" customWidth="1" min="5" max="5" width="9"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="17.59765625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="16.33203125"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="27.1328125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="25.9296875"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="17.79296875"/>
+    <col bestFit="1" customWidth="1" min="8" max="8" width="16.54296875"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="9.00390625"/>
     <col bestFit="1" customWidth="1" min="10" max="10" width="14.1328125"/>
     <col bestFit="1" customWidth="1" min="11" max="11" width="13.265625"/>
   </cols>
@@ -1859,87 +1873,99 @@
         <v>34</v>
       </c>
       <c r="C1" s="71"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="73" t="s">
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" ht="14.65">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="73" t="s">
         <v>24</v>
       </c>
       <c r="C2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="G2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="H2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="I2" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="J2" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="77" t="s">
+      <c r="K2" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="78" t="s">
+      <c r="L2" s="76" t="s">
         <v>39</v>
       </c>
+      <c r="M2" s="77" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="63">
+      <c r="B3" s="79">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="80">
         <v>0.501</v>
       </c>
-      <c r="D3" s="1">
-        <v>-1.6e-002</v>
-      </c>
-      <c r="E3" s="63">
+      <c r="D3" s="80">
+        <v>-1.9e-002</v>
+      </c>
+      <c r="E3" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="79">
         <v>0.27538000000000001</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="80">
         <v>0</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="80">
         <v>0.48499999999999999</v>
       </c>
-      <c r="H3" s="21">
-        <f t="shared" ref="H3:H8" si="2">B3*C3</f>
+      <c r="I3" s="34"/>
+      <c r="J3" s="1">
+        <f>B3*C3</f>
         <v>0.12842634</v>
       </c>
-      <c r="I3" s="65">
-        <f t="shared" ref="I3:I8" si="3">B3*D3+E3*G3</f>
-        <v>0.12945785999999998</v>
-      </c>
-      <c r="J3" s="21">
-        <f t="shared" ref="J3:J8" si="4">0.5*B3*C3^2</f>
+      <c r="K3" s="65">
+        <f>B3*D3+F3*H3</f>
+        <v>0.12868884</v>
+      </c>
+      <c r="L3" s="21">
+        <f>0.5*B3*C3^2</f>
         <v>3.2170798170000001e-002</v>
       </c>
-      <c r="K3" s="65">
-        <f t="shared" ref="K3:K8" si="5">0.5*(B3*D3^2+E3*G3^2)</f>
-        <v>3.2420941770000003e-002</v>
+      <c r="M3" s="65">
+        <f>0.5*(B3*D3^2+F3*H3^2)</f>
+        <v>3.2434399619999998e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81">
+      <c r="A4" s="82"/>
+      <c r="B4" s="13">
         <v>0.25634000000000001</v>
       </c>
       <c r="C4" s="61">
@@ -1948,179 +1974,195 @@
       <c r="D4">
         <v>-0.22900000000000001</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="15"/>
+      <c r="F4" s="13">
         <v>0.78227999999999998</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.24299999999999999</v>
       </c>
-      <c r="H4" s="26">
-        <f t="shared" si="2"/>
+      <c r="I4" s="15"/>
+      <c r="J4">
+        <f>B4*C4</f>
         <v>0.12740098</v>
       </c>
-      <c r="I4" s="60">
-        <f t="shared" si="3"/>
+      <c r="K4" s="60">
+        <f>B4*D4+F4*H4</f>
         <v>0.13139217999999997</v>
       </c>
-      <c r="J4" s="26">
-        <f t="shared" si="4"/>
+      <c r="L4" s="26">
+        <f>0.5*B4*C4^2</f>
         <v>3.1659143530000003e-002</v>
       </c>
-      <c r="K4" s="60">
-        <f t="shared" si="5"/>
+      <c r="M4" s="60">
+        <f>0.5*(B4*D4^2+F4*H4^2)</f>
         <v>2.9817788829999997e-002</v>
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="82"/>
-      <c r="B5" s="83">
+      <c r="A5" s="83"/>
+      <c r="B5" s="17">
         <v>0.76324000000000003</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="19">
         <v>0.34899999999999998</v>
       </c>
-      <c r="D5" s="67">
+      <c r="D5" s="19">
         <v>0.16600000000000001</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="20"/>
+      <c r="F5" s="84">
         <v>0.27538000000000001</v>
       </c>
-      <c r="F5" s="67">
+      <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="G5" s="67">
+      <c r="H5" s="19">
         <v>0.48499999999999999</v>
       </c>
-      <c r="H5" s="83">
-        <f t="shared" si="2"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="67">
+        <f>B5*C5</f>
         <v>0.26637075999999998</v>
       </c>
-      <c r="I5" s="69">
-        <f t="shared" si="3"/>
+      <c r="K5" s="69">
+        <f>B5*D5+F5*H5</f>
         <v>0.26025714</v>
       </c>
-      <c r="J5" s="83">
-        <f t="shared" si="4"/>
+      <c r="L5" s="85">
+        <f>0.5*B5*C5^2</f>
         <v>4.6481697619999991e-002</v>
       </c>
-      <c r="K5" s="69">
-        <f t="shared" si="5"/>
+      <c r="M5" s="69">
+        <f>0.5*(B5*D5^2+F5*H5^2)</f>
         <v>4.2904050970000003e-002</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="63">
+      <c r="A6" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="79">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="80">
         <v>0.46800000000000003</v>
       </c>
-      <c r="D6" s="65">
-        <v>0.253</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="80">
+        <v>0.221</v>
+      </c>
+      <c r="E6" s="34">
+        <v>2.4e-002</v>
+      </c>
+      <c r="F6" s="8">
         <v>0.27538000000000001</v>
       </c>
-      <c r="F6">
+      <c r="G6" s="80">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>0.253</v>
-      </c>
-      <c r="H6" s="26">
-        <f t="shared" si="2"/>
+      <c r="H6" s="80">
+        <v>0.221</v>
+      </c>
+      <c r="I6" s="34"/>
+      <c r="J6">
+        <f>B6*C6</f>
         <v>0.11996712000000001</v>
       </c>
-      <c r="I6" s="60">
-        <f t="shared" si="3"/>
-        <v>0.13452516</v>
-      </c>
-      <c r="J6" s="26">
-        <f t="shared" si="4"/>
+      <c r="K6" s="60">
+        <f>B6*D6+F6*H6</f>
+        <v>0.11751012000000001</v>
+      </c>
+      <c r="L6" s="26">
+        <f>0.5*B6*C6^2</f>
         <v>2.8072306080000005e-002</v>
       </c>
-      <c r="K6" s="60">
-        <f t="shared" si="5"/>
-        <v>1.7017432739999998e-002</v>
+      <c r="M6" s="60">
+        <f>0.5*(B6*D6^2+F6*H6^2)</f>
+        <v>1.2984868260000001e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="85"/>
-      <c r="B7" s="81">
+      <c r="A7" s="82"/>
+      <c r="B7" s="13">
         <v>0.25634000000000001</v>
       </c>
       <c r="C7">
         <v>0.56299999999999994</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="E7" s="15">
+        <v>1.2e-002</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0.78227999999999998</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E7" s="81">
-        <v>0.78227999999999998</v>
-      </c>
-      <c r="F7">
+      <c r="I7" s="15"/>
+      <c r="J7">
+        <f>B7*C7</f>
+        <v>0.14431942</v>
+      </c>
+      <c r="K7" s="60">
+        <f>B7*D7+F7*H7</f>
+        <v>0.14335608000000002</v>
+      </c>
+      <c r="L7" s="26">
+        <f>0.5*B7*C7^2</f>
+        <v>4.0625916729999996e-002</v>
+      </c>
+      <c r="M7" s="60">
+        <f>0.5*(B7*D7^2+F7*H7^2)</f>
+        <v>9.8995780800000023e-003</v>
+      </c>
+    </row>
+    <row r="8" ht="14.65">
+      <c r="A8" s="83"/>
+      <c r="B8" s="17">
+        <v>0.76324000000000003</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="E8" s="86">
+        <v>1.4999999999999999e-002</v>
+      </c>
+      <c r="F8" s="84">
+        <v>0.27538000000000001</v>
+      </c>
+      <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H7" s="26">
-        <f t="shared" si="2"/>
-        <v>0.14431942</v>
-      </c>
-      <c r="I7" s="60">
-        <f t="shared" si="3"/>
-        <v>0.1454068</v>
-      </c>
-      <c r="J7" s="26">
-        <f t="shared" si="4"/>
-        <v>4.0625916729999996e-002</v>
-      </c>
-      <c r="K7" s="60">
-        <f t="shared" si="5"/>
-        <v>1.0178476000000002e-002</v>
-      </c>
-    </row>
-    <row r="8" ht="14.65">
-      <c r="A8" s="86"/>
-      <c r="B8" s="83">
-        <v>0.76324000000000003</v>
-      </c>
-      <c r="C8" s="67">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="D8" s="69">
+      <c r="H8" s="19">
         <v>0.34399999999999997</v>
       </c>
-      <c r="E8" s="66">
-        <v>0.27538000000000001</v>
-      </c>
-      <c r="F8" s="67">
-        <v>0</v>
-      </c>
-      <c r="G8" s="67">
-        <v>0.34399999999999997</v>
-      </c>
-      <c r="H8" s="83">
-        <f t="shared" si="2"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="67">
+        <f>B8*C8</f>
         <v>0.32437700000000003</v>
       </c>
-      <c r="I8" s="69">
-        <f t="shared" si="3"/>
+      <c r="K8" s="69">
+        <f>B8*D8+F8*H8</f>
         <v>0.35728527999999998</v>
       </c>
-      <c r="J8" s="83">
-        <f t="shared" si="4"/>
+      <c r="L8" s="85">
+        <f>0.5*B8*C8^2</f>
         <v>6.8930112500000001e-002</v>
       </c>
-      <c r="K8" s="69">
-        <f t="shared" si="5"/>
+      <c r="M8" s="69">
+        <f>0.5*(B8*D8^2+F8*H8^2)</f>
         <v>6.1453068159999999e-002</v>
       </c>
     </row>
@@ -2129,8 +2171,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
   </mergeCells>
@@ -2147,30 +2189,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="88" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" s="89"/>
       <c r="C1" s="90" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1" s="89"/>
     </row>
     <row r="2">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="75" t="s">
-        <v>43</v>
+      <c r="B2" s="74" t="s">
+        <v>45</v>
       </c>
       <c r="C2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="75" t="s">
-        <v>43</v>
+      <c r="D2" s="74" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="83">
+      <c r="A3" s="85">
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="69">
@@ -2210,7 +2252,7 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="91" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -2240,7 +2282,7 @@
     </row>
     <row r="7">
       <c r="A7" s="93" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="94">
         <f>AVERAGE(B2:B6)</f>
@@ -2249,7 +2291,7 @@
     </row>
     <row r="8" ht="14.65">
       <c r="A8" s="95" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" s="96">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">Carrello rosso (kg)</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t xml:space="preserve">Energia finale (J)</t>
-  </si>
-  <si>
-    <t>0.008</t>
   </si>
   <si>
     <t>Velcro</t>
@@ -779,8 +776,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="8" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -788,16 +785,16 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="8" borderId="33" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1858,14 +1855,14 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="14.00390625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="17.79296875"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="16.54296875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="9"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="17.59765625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="17.79296875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="16.54296875"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="9.00390625"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="14.1328125"/>
+    <col customWidth="1" min="4" max="4" width="11.00390625"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="16.54296875"/>
+    <col customWidth="1" min="6" max="6" width="10.00390625"/>
+    <col bestFit="1" customWidth="1" min="7" max="8" width="17.79296875"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="16.54296875"/>
+    <col customWidth="1" min="10" max="10" width="11.875"/>
     <col bestFit="1" customWidth="1" min="11" max="11" width="13.265625"/>
+    <col bestFit="1" min="13" max="13" width="9.625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
@@ -1875,12 +1872,13 @@
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
       <c r="E1" s="71"/>
-      <c r="F1" s="72" t="s">
+      <c r="F1" s="71"/>
+      <c r="G1" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="72"/>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
     </row>
     <row r="2" ht="14.65">
       <c r="B2" s="73" t="s">
@@ -1890,33 +1888,36 @@
         <v>27</v>
       </c>
       <c r="D2" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="F2" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="G2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="H2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="I2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="J2" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="76" t="s">
+      <c r="K2" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="77" t="s">
+      <c r="L2" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="76" t="s">
+      <c r="M2" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="77" t="s">
+      <c r="N2" s="77" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1928,241 +1929,275 @@
         <v>0.25634000000000001</v>
       </c>
       <c r="C3" s="80">
-        <v>0.501</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="D3" s="80">
+        <v>2.8000000000000001e-002</v>
+      </c>
+      <c r="E3" s="80">
         <v>-1.9e-002</v>
       </c>
-      <c r="E3" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="79">
+      <c r="F3" s="34">
+        <v>8.0000000000000002e-003</v>
+      </c>
+      <c r="G3" s="9">
         <v>0.27538000000000001</v>
       </c>
-      <c r="G3" s="80">
+      <c r="H3" s="80">
         <v>0</v>
       </c>
-      <c r="H3" s="80">
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="1">
+      <c r="I3" s="80">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="J3" s="34">
+        <v>1.e-002</v>
+      </c>
+      <c r="K3" s="1">
         <f>B3*C3</f>
-        <v>0.12842634</v>
-      </c>
-      <c r="K3" s="65">
-        <f>B3*D3+F3*H3</f>
-        <v>0.12868884</v>
-      </c>
-      <c r="L3" s="21">
+        <v>0.13278412000000001</v>
+      </c>
+      <c r="L3" s="65">
+        <f>B3*E3+G3*I3</f>
+        <v>0.13034112</v>
+      </c>
+      <c r="M3" s="21">
         <f>0.5*B3*C3^2</f>
-        <v>3.2170798170000001e-002</v>
-      </c>
-      <c r="M3" s="65">
-        <f>0.5*(B3*D3^2+F3*H3^2)</f>
-        <v>3.2434399619999998e-002</v>
+        <v>3.439108708e-002</v>
+      </c>
+      <c r="N3" s="65">
+        <f>0.5*(B3*E3^2+G3*I3^2)</f>
+        <v>3.3240712259999999e-002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="82"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="13">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C4" s="61">
-        <v>0.497</v>
-      </c>
-      <c r="D4">
-        <v>-0.22900000000000001</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="13">
+      <c r="C4" s="82">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="D4" s="83">
+        <v>1.6e-002</v>
+      </c>
+      <c r="E4">
+        <v>-0.21299999999999999</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1.2999999999999999e-002</v>
+      </c>
+      <c r="G4" s="14">
         <v>0.78227999999999998</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>0.24299999999999999</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4">
+      <c r="I4" s="61">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="J4" s="15">
+        <v>4.0000000000000001e-003</v>
+      </c>
+      <c r="K4">
         <f>B4*C4</f>
-        <v>0.12740098</v>
-      </c>
-      <c r="K4" s="60">
-        <f>B4*D4+F4*H4</f>
-        <v>0.13139217999999997</v>
-      </c>
-      <c r="L4" s="26">
+        <v>0.13047706000000001</v>
+      </c>
+      <c r="L4" s="60">
+        <f>B4*E4+G4*I4</f>
+        <v>0.13314677999999996</v>
+      </c>
+      <c r="M4" s="26">
         <f>0.5*B4*C4^2</f>
-        <v>3.1659143530000003e-002</v>
-      </c>
-      <c r="M4" s="60">
-        <f>0.5*(B4*D4^2+F4*H4^2)</f>
-        <v>2.9817788829999997e-002</v>
+        <v>3.3206411769999999e-002</v>
+      </c>
+      <c r="N4" s="60">
+        <f>0.5*(B4*E4^2+G4*I4^2)</f>
+        <v>2.8344608729999998e-002</v>
       </c>
     </row>
     <row r="5" ht="14.65">
-      <c r="A5" s="83"/>
+      <c r="A5" s="84"/>
       <c r="B5" s="17">
         <v>0.76324000000000003</v>
       </c>
       <c r="C5" s="19">
-        <v>0.34899999999999998</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="D5" s="19">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="84">
+        <v>1.2999999999999999e-002</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="F5" s="85">
+        <v>1.e-002</v>
+      </c>
+      <c r="G5" s="18">
         <v>0.27538000000000001</v>
       </c>
-      <c r="G5" s="19">
+      <c r="H5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="I5">
         <v>0.48499999999999999</v>
       </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="67">
+      <c r="J5" s="20">
+        <v>1.4e-002</v>
+      </c>
+      <c r="K5" s="67">
         <f>B5*C5</f>
-        <v>0.26637075999999998</v>
-      </c>
-      <c r="K5" s="69">
-        <f>B5*D5+F5*H5</f>
-        <v>0.26025714</v>
-      </c>
-      <c r="L5" s="85">
+        <v>0.26408103999999999</v>
+      </c>
+      <c r="L5" s="69">
+        <f>B5*E5+G5*I5</f>
+        <v>0.25796742</v>
+      </c>
+      <c r="M5" s="86">
         <f>0.5*B5*C5^2</f>
-        <v>4.6481697619999991e-002</v>
-      </c>
-      <c r="M5" s="69">
-        <f>0.5*(B5*D5^2+F5*H5^2)</f>
-        <v>4.2904050970000003e-002</v>
+        <v>4.5686019919999994e-002</v>
+      </c>
+      <c r="N5" s="69">
+        <f>0.5*(B5*E5^2+G5*I5^2)</f>
+        <v>4.252739203e-002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="79">
         <v>0.25634000000000001</v>
       </c>
       <c r="C6" s="80">
-        <v>0.46800000000000003</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="D6" s="80">
-        <v>0.221</v>
-      </c>
-      <c r="E6" s="34">
+        <v>1.4e-002</v>
+      </c>
+      <c r="E6" s="80">
+        <v>0.251</v>
+      </c>
+      <c r="F6" s="34">
         <v>2.4e-002</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G6" s="80">
         <v>0.27538000000000001</v>
       </c>
-      <c r="G6" s="80">
+      <c r="H6" s="80">
         <v>0</v>
       </c>
-      <c r="H6" s="80">
-        <v>0.221</v>
-      </c>
-      <c r="I6" s="34"/>
-      <c r="J6">
+      <c r="I6" s="80">
+        <v>0.251</v>
+      </c>
+      <c r="J6" s="34">
+        <v>2.4e-002</v>
+      </c>
+      <c r="K6">
         <f>B6*C6</f>
-        <v>0.11996712000000001</v>
-      </c>
-      <c r="K6" s="60">
-        <f>B6*D6+F6*H6</f>
-        <v>0.11751012000000001</v>
-      </c>
-      <c r="L6" s="26">
+        <v>0.14585745999999999</v>
+      </c>
+      <c r="L6" s="60">
+        <f>B6*E6+G6*I6</f>
+        <v>0.13346172000000001</v>
+      </c>
+      <c r="M6" s="26">
         <f>0.5*B6*C6^2</f>
-        <v>2.8072306080000005e-002</v>
-      </c>
-      <c r="M6" s="60">
-        <f>0.5*(B6*D6^2+F6*H6^2)</f>
-        <v>1.2984868260000001e-002</v>
+        <v>4.1496447369999995e-002</v>
+      </c>
+      <c r="N6" s="60">
+        <f>0.5*(B6*E6^2+G6*I6^2)</f>
+        <v>1.6749445860000003e-002</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="82"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="13">
         <v>0.25634000000000001</v>
       </c>
       <c r="C7">
-        <v>0.56299999999999994</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="D7">
+        <v>4.0000000000000001e-003</v>
+      </c>
+      <c r="E7">
         <v>0.13200000000000001</v>
       </c>
-      <c r="E7" s="15">
+      <c r="F7" s="15">
         <v>1.2e-002</v>
       </c>
-      <c r="F7" s="13">
+      <c r="G7" s="14">
         <v>0.78227999999999998</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7">
+      <c r="I7">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J7" s="15">
+        <v>1.2e-002</v>
+      </c>
+      <c r="K7">
         <f>B7*C7</f>
-        <v>0.14431942</v>
-      </c>
-      <c r="K7" s="60">
-        <f>B7*D7+F7*H7</f>
-        <v>0.14335608000000002</v>
-      </c>
-      <c r="L7" s="26">
+        <v>0.14585745999999999</v>
+      </c>
+      <c r="L7" s="60">
+        <f>B7*E7+G7*I7</f>
+        <v>0.13709784</v>
+      </c>
+      <c r="M7" s="26">
         <f>0.5*B7*C7^2</f>
-        <v>4.0625916729999996e-002</v>
-      </c>
-      <c r="M7" s="60">
-        <f>0.5*(B7*D7^2+F7*H7^2)</f>
-        <v>9.8995780800000023e-003</v>
+        <v>4.1496447369999995e-002</v>
+      </c>
+      <c r="N7" s="60">
+        <f>0.5*(B7*E7^2+G7*I7^2)</f>
+        <v>9.048457440000001e-003</v>
       </c>
     </row>
     <row r="8" ht="14.65">
-      <c r="A8" s="83"/>
+      <c r="A8" s="84"/>
       <c r="B8" s="17">
         <v>0.76324000000000003</v>
       </c>
       <c r="C8" s="19">
-        <v>0.42499999999999999</v>
+        <v>0.47999999999999998</v>
       </c>
       <c r="D8" s="19">
+        <v>4.0000000000000001e-003</v>
+      </c>
+      <c r="E8" s="19">
         <v>0.34399999999999997</v>
       </c>
-      <c r="E8" s="86">
+      <c r="F8" s="20">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="F8" s="84">
+      <c r="G8" s="18">
         <v>0.27538000000000001</v>
       </c>
-      <c r="G8" s="19">
+      <c r="H8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="19">
+      <c r="I8" s="19">
         <v>0.34399999999999997</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="67">
+      <c r="J8" s="20">
+        <v>1.4999999999999999e-002</v>
+      </c>
+      <c r="K8" s="67">
         <f>B8*C8</f>
-        <v>0.32437700000000003</v>
-      </c>
-      <c r="K8" s="69">
-        <f>B8*D8+F8*H8</f>
+        <v>0.36635519999999999</v>
+      </c>
+      <c r="L8" s="69">
+        <f>B8*E8+G8*I8</f>
         <v>0.35728527999999998</v>
       </c>
-      <c r="L8" s="85">
+      <c r="M8" s="86">
         <f>0.5*B8*C8^2</f>
-        <v>6.8930112500000001e-002</v>
-      </c>
-      <c r="M8" s="69">
-        <f>0.5*(B8*D8^2+F8*H8^2)</f>
+        <v>8.7925247999999998e-002</v>
+      </c>
+      <c r="N8" s="69">
+        <f>0.5*(B8*E8^2+G8*I8^2)</f>
         <v>6.1453068159999999e-002</v>
       </c>
     </row>
@@ -2171,8 +2206,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
   </mergeCells>
@@ -2189,11 +2224,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="89"/>
       <c r="C1" s="90" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1" s="89"/>
     </row>
@@ -2201,29 +2236,29 @@
       <c r="A2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>45</v>
+      <c r="B2" s="75" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="74" t="s">
-        <v>45</v>
+      <c r="D2" s="75" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="85">
+      <c r="A3" s="86">
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="69">
-        <v>0.68120000000000003</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="C3" s="67">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
       <c r="D3" s="69">
-        <v>0.93589999999999995</v>
+        <v>0.93600000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -2252,7 +2287,7 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="91" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -2282,7 +2317,7 @@
     </row>
     <row r="7">
       <c r="A7" s="93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="94">
         <f>AVERAGE(B2:B6)</f>
@@ -2291,7 +2326,7 @@
     </row>
     <row r="8" ht="14.65">
       <c r="A8" s="95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="96">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -1,89 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Urti/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_2FEC3D3CD2DAA604E597749B5C2171355A12C4A4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBE31323-D30B-4F17-A401-F3B07B87B18C}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Misura masse" sheetId="1" r:id="rId1"/>
-    <sheet name="Carrello" sheetId="2" r:id="rId2"/>
-    <sheet name="Piano inclinato" sheetId="3" r:id="rId3"/>
-    <sheet name="Urto magnete e molla" sheetId="4" r:id="rId4"/>
-    <sheet name="Urti tra carrelli" sheetId="5" r:id="rId5"/>
-    <sheet name="Attrito statico" sheetId="6" r:id="rId6"/>
-    <sheet name="Attrito dinamico" sheetId="7" r:id="rId7"/>
+    <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Carrello" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Piano inclinato" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Urto magnete e molla" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Urti tra carrelli" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Attrito statico" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Attrito dinamico" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
-  <si>
-    <t>Carrello rosso (kg)</t>
-  </si>
-  <si>
-    <t>Carrello blu  (kg)</t>
-  </si>
-  <si>
-    <t>massa 1  (kg)</t>
-  </si>
-  <si>
-    <t>massa 2  (kg)</t>
-  </si>
-  <si>
-    <t>Massa totale  (kg)</t>
-  </si>
-  <si>
-    <t>massa Libro 1  (kg)</t>
-  </si>
-  <si>
-    <t>massa Libro 2  (kg)</t>
-  </si>
-  <si>
-    <t>Errore sulla massa (kg)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t xml:space="preserve">Carrello rosso (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrello blu  (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">massa 1  (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">massa 2  (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa totale  (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">massa Libro 1  (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">massa Libro 2  (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errore sulla massa (kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Massa </t>
   </si>
   <si>
-    <t>Massa con magnete</t>
-  </si>
-  <si>
-    <t>Massa con molla</t>
-  </si>
-  <si>
-    <t>Interpolazione carrello</t>
-  </si>
-  <si>
-    <t>Interpolazione carrello+masse</t>
-  </si>
-  <si>
-    <t>m (kg)</t>
-  </si>
-  <si>
-    <t>sm (kg)</t>
+    <t xml:space="preserve">Massa con magnete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa con molla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpolazione carrello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpolazione carrello+masse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sm (kg)</t>
   </si>
   <si>
     <t>x_best</t>
@@ -92,7 +75,7 @@
     <t>sx_best</t>
   </si>
   <si>
-    <t>Interpolazione piano inclinato</t>
+    <t xml:space="preserve">Interpolazione piano inclinato</t>
   </si>
   <si>
     <t>Angolo</t>
@@ -113,28 +96,22 @@
     <t>sθ</t>
   </si>
   <si>
-    <t>Massa (kg)</t>
-  </si>
-  <si>
-    <t>Area (N*s)</t>
-  </si>
-  <si>
-    <t>Incertezza (N*s)</t>
-  </si>
-  <si>
-    <t>Velocità iniziale (m/s)</t>
-  </si>
-  <si>
-    <t>Velocità finale (m/s)</t>
-  </si>
-  <si>
-    <t>Impulso (N*s)</t>
-  </si>
-  <si>
-    <t>ΔE (J)</t>
-  </si>
-  <si>
-    <t>Coeff. di restituzione</t>
+    <t xml:space="preserve">Massa (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area (N*s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (N*s) (semidisp.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velocità iniziale (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incertezza (dev.standard)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velocità finale (m/s)</t>
   </si>
   <si>
     <t>Magnete</t>
@@ -143,63 +120,60 @@
     <t>Molla</t>
   </si>
   <si>
-    <t>Carrello rosso</t>
-  </si>
-  <si>
-    <t>Carrello blu</t>
-  </si>
-  <si>
-    <t>sv (m/s)</t>
-  </si>
-  <si>
-    <t>Quantità di moto iniziale (kg*m/s)</t>
-  </si>
-  <si>
-    <t>Quantità di moto finale (kg*m/s)</t>
-  </si>
-  <si>
-    <t>Energia inizale (J)</t>
-  </si>
-  <si>
-    <t>Energia finale (J)</t>
+    <t xml:space="preserve">Carrello rosso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrello blu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sv (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantità di moto iniziale (kg*m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantità di moto finale (kg*m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energia inizale (J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energia finale (J)</t>
   </si>
   <si>
     <t>Velcro</t>
   </si>
   <si>
-    <t>1 libro</t>
-  </si>
-  <si>
-    <t>2 libri</t>
-  </si>
-  <si>
-    <t>F (N)</t>
-  </si>
-  <si>
-    <t>Coefficiente angolare</t>
+    <t xml:space="preserve">1 libro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 libri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F (N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coefficiente angolare</t>
   </si>
   <si>
     <t>Media</t>
   </si>
   <si>
-    <t>Errore della media</t>
-  </si>
-  <si>
-    <t>Incertezza (semidispersione)</t>
+    <t xml:space="preserve">Errore della media</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -263,49 +237,49 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+  <borders count="42">
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -315,7 +289,7 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -330,7 +304,7 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -342,50 +316,50 @@
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -394,27 +368,27 @@
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -423,124 +397,124 @@
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -555,10 +529,10 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -568,23 +542,23 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -594,56 +568,98 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -655,8 +671,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -665,9 +681,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -676,167 +692,170 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="98">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="99">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="7" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="27" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="36" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="2" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="8" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="37" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="10" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="10" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf fontId="0" fillId="10" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="8" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -854,8 +873,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1066,30 +1368,31 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Foglio1"/>
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr codeName="Foglio1">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.53125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.9296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16.06640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.265625" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="16.86328125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="15.46484375"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="13.9296875"/>
+    <col bestFit="1" customWidth="1" min="4" max="5" width="11.53125"/>
+    <col bestFit="1" customWidth="1" min="6" max="6" width="14.9296875"/>
+    <col bestFit="1" customWidth="1" min="7" max="8" width="16.06640625"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="19.265625"/>
+    <col bestFit="1" customWidth="1" min="10" max="10" width="11.46484375"/>
+    <col bestFit="1" customWidth="1" min="11" max="12" width="18.3984375"/>
+    <col bestFit="1" customWidth="1" min="13" max="13" width="13.1328125"/>
+    <col bestFit="1" customWidth="1" min="14" max="14" width="9.265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1116,7 +1419,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
@@ -1141,10 +1444,10 @@
         <v>0.18593999999999999</v>
       </c>
       <c r="I2" s="11">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+        <v>5.0000000000000001e-004</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
@@ -1160,7 +1463,7 @@
       </c>
       <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1177,138 +1480,142 @@
       <c r="G4" s="19"/>
       <c r="H4" s="20"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15">
       <c r="O15" s="14"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16">
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
       <c r="Q16" s="14"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Foglio2"/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr codeName="Foglio2">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="11.53125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12.73046875" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" customWidth="1"/>
+    <col customWidth="1" min="2" max="2" width="11.53125"/>
+    <col customWidth="1" min="3" max="3" width="12"/>
+    <col customWidth="1" min="4" max="4" width="12.73046875"/>
+    <col customWidth="1" min="5" max="5" width="13.53125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" s="21"/>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="76" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="77"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23" t="s">
+      <c r="E1" s="25"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="27">
+    <row r="3">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>0.249</v>
       </c>
-      <c r="C3" s="28">
-        <v>0.04</v>
-      </c>
-      <c r="D3" s="29">
+      <c r="C3" s="32">
+        <v>4.0000000000000001e-002</v>
+      </c>
+      <c r="D3" s="33">
         <v>0.76900000000000002</v>
       </c>
-      <c r="E3" s="30">
-        <v>4.2999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="31">
+      <c r="E3" s="34">
+        <v>4.2999999999999997e-002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35">
         <v>2</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="36">
         <v>0.253</v>
       </c>
-      <c r="C4" s="33">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="D4" s="34">
+      <c r="C4" s="37">
+        <v>4.2999999999999997e-002</v>
+      </c>
+      <c r="D4" s="38">
         <v>0.755</v>
       </c>
       <c r="E4" s="15">
-        <v>3.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="31">
+        <v>3.7999999999999999e-002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35">
         <v>3</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="36">
         <v>0.247</v>
       </c>
-      <c r="C5" s="35">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D5" s="34">
+      <c r="C5" s="39">
+        <v>4.2000000000000003e-002</v>
+      </c>
+      <c r="D5" s="38">
         <v>0.749</v>
       </c>
       <c r="E5" s="15">
-        <v>3.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="36" t="s">
+        <v>3.7999999999999999e-002</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="41">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.24959417617111146</v>
       </c>
-      <c r="C6" s="79"/>
-      <c r="D6" s="80">
+      <c r="C6" s="42"/>
+      <c r="D6" s="43">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.75677401789187093</v>
       </c>
-      <c r="E6" s="81"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="37" t="s">
+      <c r="E6" s="44"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="82">
+      <c r="B7" s="46">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
-        <v>2.4023430034058289E-2</v>
-      </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="84">
+        <v>2.4023430034058289e-002</v>
+      </c>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
-        <v>2.2786940380104245E-2</v>
-      </c>
-      <c r="E7" s="85"/>
+        <v>2.2786940380104245e-002</v>
+      </c>
+      <c r="E7" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1319,133 +1626,137 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Foglio3"/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr codeName="Foglio3">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" s="21"/>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="38" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="54" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="22"/>
-      <c r="B2" s="40" t="s">
+    <row r="2">
+      <c r="A2" s="26"/>
+      <c r="B2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="43">
+      <c r="F2" s="58">
         <v>10</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="59">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="27">
+    <row r="3">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
       <c r="B3">
         <v>0.26400000000000001</v>
       </c>
       <c r="C3">
-        <v>2E-3</v>
+        <v>2.e-003</v>
       </c>
       <c r="D3">
         <v>0.17599999999999999</v>
       </c>
-      <c r="E3" s="45">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="31">
+      <c r="E3" s="60">
+        <v>2.e-003</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35">
         <v>2</v>
       </c>
       <c r="B4">
         <v>0.25700000000000001</v>
       </c>
       <c r="C4">
-        <v>2E-3</v>
-      </c>
-      <c r="D4" s="46">
+        <v>2.e-003</v>
+      </c>
+      <c r="D4" s="61">
         <v>0.16</v>
       </c>
-      <c r="E4" s="45">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="31">
+      <c r="E4" s="60">
+        <v>3.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.26</v>
+        <v>0.26000000000000001</v>
       </c>
       <c r="C5">
-        <v>3.0000000000000001E-3</v>
+        <v>3.0000000000000001e-003</v>
       </c>
       <c r="D5">
         <v>0.17499999999999999</v>
       </c>
-      <c r="E5" s="45">
-        <v>2.3E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="36" t="s">
+      <c r="E5" s="60">
+        <v>2.3e-003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="41">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.26040909090909087</v>
       </c>
-      <c r="C6" s="79"/>
-      <c r="D6" s="80">
+      <c r="C6" s="42"/>
+      <c r="D6" s="43">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.17242493080080176</v>
       </c>
-      <c r="E6" s="81"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="36" t="s">
+      <c r="E6" s="44"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="41">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
-        <v>1.2792042981336627E-3</v>
-      </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="80">
+        <v>1.2792042981336627e-003</v>
+      </c>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
-        <v>1.3482195315735518E-3</v>
-      </c>
-      <c r="E7" s="81"/>
+        <v>1.3482195315735518e-003</v>
+      </c>
+      <c r="E7" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1455,280 +1766,253 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Foglio4"/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr codeName="Foglio4">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.06640625" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="7.3984375"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="9.54296875"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="9.125"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="22.953125"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="17.79296875"/>
+    <col customWidth="1" min="6" max="6" width="15.06640625"/>
+    <col bestFit="1" customWidth="1" min="7" max="7" width="16.33203125"/>
+    <col customWidth="1" min="8" max="8" width="16"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="17"/>
+    <col bestFit="1" customWidth="1" min="11" max="11" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="47" t="s">
+    <row r="1" ht="28.5">
+      <c r="B1" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="97" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="47" t="s">
+      <c r="F1" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="97" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="47" t="s">
+      <c r="G1" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="47" t="s">
+      <c r="H1" s="64" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="47" t="s">
+      <c r="B2" s="14">
+        <v>0.27538000000000001</v>
+      </c>
+      <c r="C2" s="65">
+        <v>-0.26100000000000001</v>
+      </c>
+      <c r="D2" s="65">
+        <v>2.e-002</v>
+      </c>
+      <c r="E2" s="65">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="F2" s="65">
+        <v>8.0000000000000002e-003</v>
+      </c>
+      <c r="G2" s="65">
+        <v>-0.54100000000000004</v>
+      </c>
+      <c r="H2" s="66">
+        <v>7.0000000000000001e-003</v>
+      </c>
+    </row>
+    <row r="3" ht="14.65">
+      <c r="A3" s="62" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="48">
-        <v>0.25634000000000001</v>
-      </c>
-      <c r="C2" s="1">
-        <v>-0.128</v>
-      </c>
-      <c r="D2" s="1">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.52700000000000002</v>
-      </c>
-      <c r="F2" s="95">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="G2" s="1">
-        <v>-1.4999999999999999E-2</v>
-      </c>
-      <c r="H2" s="95">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I2" s="49">
-        <f>B2*(G2-E2)</f>
-        <v>-0.13893628000000002</v>
-      </c>
-      <c r="J2" s="1">
-        <f>0.5*B2*(G2-E2)^2</f>
-        <v>3.7651731880000004E-2</v>
-      </c>
-      <c r="K2" s="50">
-        <f>-(B2*G2)/(B2*E2)</f>
-        <v>2.8462998102466792E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="51">
+      <c r="B3" s="67">
         <v>0.25686999999999999</v>
       </c>
-      <c r="C3" s="52">
-        <v>-0.28999999999999998</v>
-      </c>
-      <c r="D3" s="52">
-        <f>0.07/SQRT(3)</f>
-        <v>4.0414518843273808E-2</v>
-      </c>
-      <c r="E3" s="52">
-        <v>0.64100000000000001</v>
-      </c>
-      <c r="F3" s="96">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="G3" s="52">
-        <v>-0.627</v>
-      </c>
-      <c r="H3" s="96">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="I3" s="53">
-        <f>0.25687*(G3-E3)</f>
-        <v>-0.32571116</v>
-      </c>
-      <c r="J3" s="52">
-        <f>0.5*B3*(G3-E3)^2</f>
-        <v>0.20650087544000001</v>
-      </c>
-      <c r="K3" s="54">
-        <f>-(B3*G3)/(B3*E3)</f>
-        <v>0.97815912636505453</v>
+      <c r="C3" s="68">
+        <v>-0.28599999999999998</v>
+      </c>
+      <c r="D3" s="68">
+        <f>0.04</f>
+        <v>4.0000000000000001e-002</v>
+      </c>
+      <c r="E3" s="69">
+        <v>0.64000000000000001</v>
+      </c>
+      <c r="F3" s="68">
+        <v>7.0000000000000001e-003</v>
+      </c>
+      <c r="G3" s="68">
+        <v>-0.624</v>
+      </c>
+      <c r="H3" s="70">
+        <v>6.0000000000000001e-003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="16.53125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="8" width="17.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.53125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.86328125" customWidth="1"/>
-    <col min="11" max="11" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.59765625" bestFit="1"/>
+    <col customWidth="1" min="2" max="2" width="14"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="17.796875"/>
+    <col customWidth="1" min="4" max="4" width="11"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="16.53125"/>
+    <col customWidth="1" min="6" max="6" width="10"/>
+    <col bestFit="1" customWidth="1" min="7" max="8" width="17.796875"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" width="16.53125"/>
+    <col customWidth="1" min="10" max="10" width="11.86328125"/>
+    <col bestFit="1" customWidth="1" min="11" max="11" width="13.265625"/>
+    <col bestFit="1" min="13" max="13" width="9.59765625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B1" s="89" t="s">
+    <row r="1">
+      <c r="B1" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="91" t="s">
+      <c r="E2" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="56" t="s">
+      <c r="L2" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="58" t="s">
+      <c r="M2" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="59" t="s">
+      <c r="N2" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="59" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="60">
+    </row>
+    <row r="3">
+      <c r="A3" s="79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="80">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="81">
         <v>0.51800000000000002</v>
       </c>
-      <c r="D3" s="61">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="E3" s="61">
-        <v>-1.9E-2</v>
-      </c>
-      <c r="F3" s="30">
-        <v>8.0000000000000002E-3</v>
+      <c r="D3" s="81">
+        <v>2.8000000000000001e-002</v>
+      </c>
+      <c r="E3" s="81">
+        <v>-1.9e-002</v>
+      </c>
+      <c r="F3" s="34">
+        <v>8.0000000000000002e-003</v>
       </c>
       <c r="G3" s="9">
         <v>0.27538000000000001</v>
       </c>
-      <c r="H3" s="61">
+      <c r="H3" s="81">
         <v>0</v>
       </c>
-      <c r="I3" s="61">
+      <c r="I3" s="81">
         <v>0.49099999999999999</v>
       </c>
-      <c r="J3" s="30">
-        <v>0.01</v>
+      <c r="J3" s="34">
+        <v>1.e-002</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" ref="K3:K8" si="0">B3*C3</f>
         <v>0.13278412000000001</v>
       </c>
-      <c r="L3" s="50">
+      <c r="L3" s="82">
         <f t="shared" ref="L3:L8" si="1">B3*E3+G3*I3</f>
         <v>0.13034112</v>
       </c>
       <c r="M3" s="21">
         <f t="shared" ref="M3:M8" si="2">0.5*B3*C3^2</f>
-        <v>3.439108708E-2</v>
-      </c>
-      <c r="N3" s="50">
+        <v>3.439108708e-002</v>
+      </c>
+      <c r="N3" s="82">
         <f t="shared" ref="N3:N8" si="3">0.5*(B3*E3^2+G3*I3^2)</f>
-        <v>3.3240712259999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="93"/>
+        <v>3.3240712259999999e-002</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="83"/>
       <c r="B4" s="13">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="61">
         <v>0.50900000000000001</v>
       </c>
       <c r="D4">
-        <v>1.6E-2</v>
+        <v>1.6e-002</v>
       </c>
       <c r="E4">
         <v>-0.21299999999999999</v>
       </c>
       <c r="F4" s="15">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2999999999999999e-002</v>
       </c>
       <c r="G4" s="14">
         <v>0.78227999999999998</v>
@@ -1736,31 +2020,31 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="46">
-        <v>0.24</v>
+      <c r="I4" s="61">
+        <v>0.23999999999999999</v>
       </c>
       <c r="J4" s="15">
-        <v>4.0000000000000001E-3</v>
+        <v>4.0000000000000001e-003</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
         <v>0.13047706000000001</v>
       </c>
-      <c r="L4" s="45">
+      <c r="L4" s="60">
         <f t="shared" si="1"/>
         <v>0.13314677999999996</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="26">
         <f t="shared" si="2"/>
-        <v>3.3206411769999999E-2</v>
-      </c>
-      <c r="N4" s="45">
+        <v>3.3206411769999999e-002</v>
+      </c>
+      <c r="N4" s="60">
         <f t="shared" si="3"/>
-        <v>2.8344608729999998E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="94"/>
+        <v>2.8344608729999998e-002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="84"/>
       <c r="B5" s="17">
         <v>0.76324000000000003</v>
       </c>
@@ -1768,13 +2052,13 @@
         <v>0.34599999999999997</v>
       </c>
       <c r="D5" s="19">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2999999999999999e-002</v>
       </c>
       <c r="E5" s="19">
         <v>0.16300000000000001</v>
       </c>
-      <c r="F5" s="62">
-        <v>0.01</v>
+      <c r="F5" s="85">
+        <v>1.e-002</v>
       </c>
       <c r="G5" s="18">
         <v>0.27538000000000001</v>
@@ -1786,75 +2070,75 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="J5" s="20">
-        <v>1.4E-2</v>
-      </c>
-      <c r="K5" s="52">
+        <v>1.4e-002</v>
+      </c>
+      <c r="K5" s="86">
         <f t="shared" si="0"/>
         <v>0.26408103999999999</v>
       </c>
-      <c r="L5" s="54">
+      <c r="L5" s="87">
         <f t="shared" si="1"/>
         <v>0.25796742</v>
       </c>
-      <c r="M5" s="63">
+      <c r="M5" s="88">
         <f t="shared" si="2"/>
-        <v>4.5686019919999994E-2</v>
-      </c>
-      <c r="N5" s="54">
+        <v>4.5686019919999994e-002</v>
+      </c>
+      <c r="N5" s="87">
         <f t="shared" si="3"/>
-        <v>4.252739203E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="60">
+        <v>4.252739203e-002</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="80">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="81">
         <v>0.56899999999999995</v>
       </c>
-      <c r="D6" s="61">
-        <v>1.4E-2</v>
-      </c>
-      <c r="E6" s="61">
+      <c r="D6" s="81">
+        <v>1.4e-002</v>
+      </c>
+      <c r="E6" s="81">
         <v>0.251</v>
       </c>
-      <c r="F6" s="30">
-        <v>2.4E-2</v>
-      </c>
-      <c r="G6" s="61">
+      <c r="F6" s="34">
+        <v>2.4e-002</v>
+      </c>
+      <c r="G6" s="81">
         <v>0.27538000000000001</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="81">
         <v>0</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="81">
         <v>0.251</v>
       </c>
-      <c r="J6" s="30">
-        <v>2.4E-2</v>
+      <c r="J6" s="34">
+        <v>2.4e-002</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
         <v>0.14585745999999999</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="60">
         <f t="shared" si="1"/>
         <v>0.13346172000000001</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="26">
         <f t="shared" si="2"/>
-        <v>4.1496447369999995E-2</v>
-      </c>
-      <c r="N6" s="45">
+        <v>4.1496447369999995e-002</v>
+      </c>
+      <c r="N6" s="60">
         <f t="shared" si="3"/>
-        <v>1.6749445860000003E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="93"/>
+        <v>1.6749445860000003e-002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="83"/>
       <c r="B7" s="13">
         <v>0.25634000000000001</v>
       </c>
@@ -1862,13 +2146,13 @@
         <v>0.56899999999999995</v>
       </c>
       <c r="D7">
-        <v>4.0000000000000001E-3</v>
+        <v>4.0000000000000001e-003</v>
       </c>
       <c r="E7">
         <v>0.13200000000000001</v>
       </c>
       <c r="F7" s="15">
-        <v>1.2E-2</v>
+        <v>1.2e-002</v>
       </c>
       <c r="G7" s="14">
         <v>0.78227999999999998</v>
@@ -1880,41 +2164,41 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="J7" s="15">
-        <v>1.2E-2</v>
+        <v>1.2e-002</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
         <v>0.14585745999999999</v>
       </c>
-      <c r="L7" s="45">
+      <c r="L7" s="60">
         <f t="shared" si="1"/>
         <v>0.13709784</v>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="26">
         <f t="shared" si="2"/>
-        <v>4.1496447369999995E-2</v>
-      </c>
-      <c r="N7" s="45">
+        <v>4.1496447369999995e-002</v>
+      </c>
+      <c r="N7" s="60">
         <f t="shared" si="3"/>
-        <v>9.048457440000001E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="94"/>
+        <v>9.048457440000001e-003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="84"/>
       <c r="B8" s="17">
         <v>0.76324000000000003</v>
       </c>
       <c r="C8" s="19">
-        <v>0.48</v>
+        <v>0.47999999999999998</v>
       </c>
       <c r="D8" s="19">
-        <v>4.0000000000000001E-3</v>
+        <v>4.0000000000000001e-003</v>
       </c>
       <c r="E8" s="19">
         <v>0.34399999999999997</v>
       </c>
       <c r="F8" s="20">
-        <v>1.4999999999999999E-2</v>
+        <v>1.4999999999999999e-002</v>
       </c>
       <c r="G8" s="18">
         <v>0.27538000000000001</v>
@@ -1926,27 +2210,27 @@
         <v>0.34399999999999997</v>
       </c>
       <c r="J8" s="20">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="K8" s="52">
+        <v>1.4999999999999999e-002</v>
+      </c>
+      <c r="K8" s="86">
         <f t="shared" si="0"/>
         <v>0.36635519999999999</v>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="87">
         <f t="shared" si="1"/>
         <v>0.35728527999999998</v>
       </c>
-      <c r="M8" s="63">
+      <c r="M8" s="88">
         <f t="shared" si="2"/>
-        <v>8.7925247999999998E-2</v>
-      </c>
-      <c r="N8" s="54">
+        <v>8.7925247999999998e-002</v>
+      </c>
+      <c r="N8" s="87">
         <f t="shared" si="3"/>
-        <v>6.1453068159999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="64"/>
+        <v>6.1453068159999999e-002</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1955,52 +2239,53 @@
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="71" t="s">
+    <row r="1">
+      <c r="A1" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="91"/>
+      <c r="C1" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="91"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="74" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="72"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="55" t="s">
+      <c r="C2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="63">
+      <c r="D2" s="76" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="88">
         <v>0.29006999999999999</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="87">
         <v>0.68100000000000005</v>
       </c>
-      <c r="C3" s="52">
+      <c r="C3" s="86">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
-      <c r="D3" s="54">
+      <c r="D3" s="87">
         <v>0.93600000000000005</v>
       </c>
     </row>
@@ -2009,72 +2294,78 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr codeName="Foglio5"/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr codeName="Foglio5">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.46484375" customWidth="1"/>
-    <col min="2" max="3" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="18.46484375"/>
+    <col bestFit="1" customWidth="1" min="2" max="3" width="16.9296875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B1" s="65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B2" s="66">
+    <row r="1">
+      <c r="B1" s="93" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="94">
         <v>1.478</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B3" s="66">
+    <row r="3">
+      <c r="B3" s="94">
         <v>1.5192000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B4" s="66">
+    <row r="4">
+      <c r="B4" s="94">
         <v>1.5113000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" s="66">
+    <row r="5">
+      <c r="B5" s="94">
         <v>1.5176000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="66">
+    <row r="6">
+      <c r="B6" s="94">
         <v>1.5246999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="67" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="68">
+    <row r="7">
+      <c r="A7" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="96">
         <f>AVERAGE(B2:B6)</f>
         <v>1.5101600000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="70">
+    <row r="8">
+      <c r="A8" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="98">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>
-        <v>8.3188100110532705E-3</v>
+        <v>8.3188100110532705e-003</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -2082,7 +2373,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB146277-E2E3-4D76-8D30-7199B5C8E298}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="EB146277-E2E3-4D76-8D30-7199B5C8E298">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">Carrello rosso (kg)</t>
   </si>
@@ -127,18 +127,6 @@
   </si>
   <si>
     <t xml:space="preserve">sv (m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantità di moto iniziale (kg*m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantità di moto finale (kg*m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energia inizale (J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energia finale (J)</t>
   </si>
   <si>
     <t>Velcro</t>
@@ -702,7 +690,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="97">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -795,6 +783,7 @@
     <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -820,14 +809,11 @@
     <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="8" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -835,9 +821,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -850,6 +833,9 @@
     <xf fontId="0" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="10" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="8" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1715,7 +1701,7 @@
       <c r="A5" s="35">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="61">
         <v>0.26000000000000001</v>
       </c>
       <c r="C5">
@@ -1724,7 +1710,7 @@
       <c r="D5">
         <v>0.17499999999999999</v>
       </c>
-      <c r="E5" s="60">
+      <c r="E5" s="62">
         <v>2.3e-003</v>
       </c>
     </row>
@@ -1794,78 +1780,78 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="65" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="14">
         <v>0.27538000000000001</v>
       </c>
-      <c r="C2" s="65">
+      <c r="C2" s="66">
         <v>-0.26100000000000001</v>
       </c>
-      <c r="D2" s="65">
+      <c r="D2" s="66">
         <v>2.e-002</v>
       </c>
-      <c r="E2" s="65">
+      <c r="E2" s="66">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F2" s="65">
+      <c r="F2" s="66">
         <v>8.0000000000000002e-003</v>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="66">
         <v>-0.54100000000000004</v>
       </c>
-      <c r="H2" s="66">
+      <c r="H2" s="67">
         <v>7.0000000000000001e-003</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="67">
+      <c r="B3" s="68">
         <v>0.25686999999999999</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="69">
         <v>-0.28599999999999998</v>
       </c>
-      <c r="D3" s="68">
+      <c r="D3" s="69">
         <f>0.04</f>
         <v>4.0000000000000001e-002</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="70">
         <v>0.64000000000000001</v>
       </c>
-      <c r="F3" s="68">
+      <c r="F3" s="69">
         <v>7.0000000000000001e-003</v>
       </c>
-      <c r="G3" s="68">
+      <c r="G3" s="69">
         <v>-0.624</v>
       </c>
-      <c r="H3" s="70">
+      <c r="H3" s="71">
         <v>6.0000000000000001e-003</v>
       </c>
     </row>
@@ -1894,75 +1880,63 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
     </row>
     <row r="2">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="62" t="s">
+      <c r="I2" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="75" t="s">
+      <c r="J2" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="77" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="78" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="80">
+      <c r="B3" s="79">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C3" s="81">
+      <c r="C3" s="80">
         <v>0.51800000000000002</v>
       </c>
-      <c r="D3" s="81">
+      <c r="D3" s="80">
         <v>2.8000000000000001e-002</v>
       </c>
-      <c r="E3" s="81">
+      <c r="E3" s="80">
         <v>-1.9e-002</v>
       </c>
       <c r="F3" s="34">
@@ -1971,34 +1945,18 @@
       <c r="G3" s="9">
         <v>0.27538000000000001</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="80">
         <v>0</v>
       </c>
-      <c r="I3" s="81">
+      <c r="I3" s="80">
         <v>0.49099999999999999</v>
       </c>
       <c r="J3" s="34">
         <v>1.e-002</v>
       </c>
-      <c r="K3" s="1">
-        <f t="shared" ref="K3:K8" si="0">B3*C3</f>
-        <v>0.13278412000000001</v>
-      </c>
-      <c r="L3" s="82">
-        <f t="shared" ref="L3:L8" si="1">B3*E3+G3*I3</f>
-        <v>0.13034112</v>
-      </c>
-      <c r="M3" s="21">
-        <f t="shared" ref="M3:M8" si="2">0.5*B3*C3^2</f>
-        <v>3.439108708e-002</v>
-      </c>
-      <c r="N3" s="82">
-        <f t="shared" ref="N3:N8" si="3">0.5*(B3*E3^2+G3*I3^2)</f>
-        <v>3.3240712259999999e-002</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="83"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="13">
         <v>0.25634000000000001</v>
       </c>
@@ -2026,25 +1984,9 @@
       <c r="J4" s="15">
         <v>4.0000000000000001e-003</v>
       </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>0.13047706000000001</v>
-      </c>
-      <c r="L4" s="60">
-        <f t="shared" si="1"/>
-        <v>0.13314677999999996</v>
-      </c>
-      <c r="M4" s="26">
-        <f t="shared" si="2"/>
-        <v>3.3206411769999999e-002</v>
-      </c>
-      <c r="N4" s="60">
-        <f t="shared" si="3"/>
-        <v>2.8344608729999998e-002</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="84"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="17">
         <v>0.76324000000000003</v>
       </c>
@@ -2057,7 +1999,7 @@
       <c r="E5" s="19">
         <v>0.16300000000000001</v>
       </c>
-      <c r="F5" s="85">
+      <c r="F5" s="83">
         <v>1.e-002</v>
       </c>
       <c r="G5" s="18">
@@ -2072,73 +2014,41 @@
       <c r="J5" s="20">
         <v>1.4e-002</v>
       </c>
-      <c r="K5" s="86">
-        <f t="shared" si="0"/>
-        <v>0.26408103999999999</v>
-      </c>
-      <c r="L5" s="87">
-        <f t="shared" si="1"/>
-        <v>0.25796742</v>
-      </c>
-      <c r="M5" s="88">
-        <f t="shared" si="2"/>
-        <v>4.5686019919999994e-002</v>
-      </c>
-      <c r="N5" s="87">
-        <f t="shared" si="3"/>
-        <v>4.252739203e-002</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="79" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="80">
+      <c r="A6" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="79">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="80">
         <v>0.56899999999999995</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="80">
         <v>1.4e-002</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="80">
         <v>0.251</v>
       </c>
       <c r="F6" s="34">
         <v>2.4e-002</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="80">
         <v>0.27538000000000001</v>
       </c>
-      <c r="H6" s="81">
+      <c r="H6" s="80">
         <v>0</v>
       </c>
-      <c r="I6" s="81">
+      <c r="I6" s="80">
         <v>0.251</v>
       </c>
       <c r="J6" s="34">
         <v>2.4e-002</v>
       </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0.14585745999999999</v>
-      </c>
-      <c r="L6" s="60">
-        <f t="shared" si="1"/>
-        <v>0.13346172000000001</v>
-      </c>
-      <c r="M6" s="26">
-        <f t="shared" si="2"/>
-        <v>4.1496447369999995e-002</v>
-      </c>
-      <c r="N6" s="60">
-        <f t="shared" si="3"/>
-        <v>1.6749445860000003e-002</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="83"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="13">
         <v>0.25634000000000001</v>
       </c>
@@ -2166,25 +2076,9 @@
       <c r="J7" s="15">
         <v>1.2e-002</v>
       </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0.14585745999999999</v>
-      </c>
-      <c r="L7" s="60">
-        <f t="shared" si="1"/>
-        <v>0.13709784</v>
-      </c>
-      <c r="M7" s="26">
-        <f t="shared" si="2"/>
-        <v>4.1496447369999995e-002</v>
-      </c>
-      <c r="N7" s="60">
-        <f t="shared" si="3"/>
-        <v>9.048457440000001e-003</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="84"/>
+      <c r="A8" s="82"/>
       <c r="B8" s="17">
         <v>0.76324000000000003</v>
       </c>
@@ -2212,25 +2106,9 @@
       <c r="J8" s="20">
         <v>1.4999999999999999e-002</v>
       </c>
-      <c r="K8" s="86">
-        <f t="shared" si="0"/>
-        <v>0.36635519999999999</v>
-      </c>
-      <c r="L8" s="87">
-        <f t="shared" si="1"/>
-        <v>0.35728527999999998</v>
-      </c>
-      <c r="M8" s="88">
-        <f t="shared" si="2"/>
-        <v>8.7925247999999998e-002</v>
-      </c>
-      <c r="N8" s="87">
-        <f t="shared" si="3"/>
-        <v>6.1453068159999999e-002</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="89"/>
+      <c r="A9" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2251,41 +2129,41 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="90" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="91"/>
+      <c r="A1" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="87" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="86"/>
     </row>
     <row r="2">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="62" t="s">
+      <c r="B2" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="76" t="s">
-        <v>42</v>
+      <c r="D2" s="77" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="88">
         <v>0.29006999999999999</v>
       </c>
-      <c r="B3" s="87">
+      <c r="B3" s="89">
         <v>0.68100000000000005</v>
       </c>
-      <c r="C3" s="86">
+      <c r="C3" s="90">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
-      <c r="D3" s="87">
+      <c r="D3" s="89">
         <v>0.93600000000000005</v>
       </c>
     </row>
@@ -2314,49 +2192,49 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="93" t="s">
-        <v>43</v>
+      <c r="B1" s="91" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="94">
+      <c r="B2" s="92">
         <v>1.478</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="94">
+      <c r="B3" s="92">
         <v>1.5192000000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="94">
+      <c r="B4" s="92">
         <v>1.5113000000000001</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="94">
+      <c r="B5" s="92">
         <v>1.5176000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="94">
+      <c r="B6" s="92">
         <v>1.5246999999999999</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="95" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="96">
+      <c r="A7" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="94">
         <f>AVERAGE(B2:B6)</f>
         <v>1.5101600000000002</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="97" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="98">
+      <c r="A8" s="95" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="96">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>
         <v>8.3188100110532705e-003</v>
       </c>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
@@ -1466,6 +1466,9 @@
       <c r="G4" s="19"/>
       <c r="H4" s="20"/>
     </row>
+    <row r="7" ht="14.25">
+      <c r="F7" s="14"/>
+    </row>
     <row r="15">
       <c r="O15" s="14"/>
     </row>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -1,72 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Urti/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A17223F8177C2D7C57AFC4E2DF361A09DF181B28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA26FCAD-1D36-4FE8-8DBD-3EA9885CC08C}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="1688" yWindow="2670" windowWidth="16200" windowHeight="9307" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Misura masse" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Carrello" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Piano inclinato" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Urto magnete e molla" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Urti tra carrelli" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Attrito statico" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="Attrito dinamico" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Misura masse" sheetId="1" r:id="rId1"/>
+    <sheet name="Carrello" sheetId="2" r:id="rId2"/>
+    <sheet name="Piano inclinato" sheetId="3" r:id="rId3"/>
+    <sheet name="Urto magnete e molla" sheetId="4" r:id="rId4"/>
+    <sheet name="Urti tra carrelli" sheetId="5" r:id="rId5"/>
+    <sheet name="Attrito statico" sheetId="6" r:id="rId6"/>
+    <sheet name="Attrito dinamico" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t xml:space="preserve">Carrello rosso (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrello blu  (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">massa 1  (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">massa 2  (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa totale  (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">massa Libro 1  (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">massa Libro 2  (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Errore sulla massa (kg)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+  <si>
+    <t>Carrello rosso (kg)</t>
+  </si>
+  <si>
+    <t>Carrello blu  (kg)</t>
+  </si>
+  <si>
+    <t>massa 1  (kg)</t>
+  </si>
+  <si>
+    <t>massa 2  (kg)</t>
+  </si>
+  <si>
+    <t>Massa totale  (kg)</t>
+  </si>
+  <si>
+    <t>massa Libro 1  (kg)</t>
+  </si>
+  <si>
+    <t>massa Libro 2  (kg)</t>
+  </si>
+  <si>
+    <t>Errore sulla massa (kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Massa </t>
   </si>
   <si>
-    <t xml:space="preserve">Massa con magnete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massa con molla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpolazione carrello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interpolazione carrello+masse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sm (kg)</t>
+    <t>Massa con magnete</t>
+  </si>
+  <si>
+    <t>Massa con molla</t>
+  </si>
+  <si>
+    <t>Interpolazione carrello</t>
+  </si>
+  <si>
+    <t>Interpolazione carrello+masse</t>
+  </si>
+  <si>
+    <t>m (kg)</t>
+  </si>
+  <si>
+    <t>sm (kg)</t>
   </si>
   <si>
     <t>x_best</t>
@@ -75,7 +92,7 @@
     <t>sx_best</t>
   </si>
   <si>
-    <t xml:space="preserve">Interpolazione piano inclinato</t>
+    <t>Interpolazione piano inclinato</t>
   </si>
   <si>
     <t>Angolo</t>
@@ -96,22 +113,22 @@
     <t>sθ</t>
   </si>
   <si>
-    <t xml:space="preserve">Massa (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Area (N*s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (N*s) (semidisp.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velocità iniziale (m/s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incertezza (dev.standard)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velocità finale (m/s)</t>
+    <t>Massa (kg)</t>
+  </si>
+  <si>
+    <t>Area (N*s)</t>
+  </si>
+  <si>
+    <t>Incertezza (N*s) (semidisp.)</t>
+  </si>
+  <si>
+    <t>Velocità iniziale (m/s)</t>
+  </si>
+  <si>
+    <t>Incertezza (dev.standard)</t>
+  </si>
+  <si>
+    <t>Velocità finale (m/s)</t>
   </si>
   <si>
     <t>Magnete</t>
@@ -120,48 +137,48 @@
     <t>Molla</t>
   </si>
   <si>
-    <t xml:space="preserve">Carrello rosso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrello blu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sv (m/s)</t>
+    <t>Carrello rosso</t>
+  </si>
+  <si>
+    <t>Carrello blu</t>
+  </si>
+  <si>
+    <t>sv (m/s)</t>
   </si>
   <si>
     <t>Velcro</t>
   </si>
   <si>
-    <t xml:space="preserve">1 libro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 libri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F (N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coefficiente angolare</t>
+    <t>1 libro</t>
+  </si>
+  <si>
+    <t>2 libri</t>
+  </si>
+  <si>
+    <t>F (N)</t>
+  </si>
+  <si>
+    <t>Coefficiente angolare</t>
   </si>
   <si>
     <t>Media</t>
   </si>
   <si>
-    <t xml:space="preserve">Errore della media</t>
+    <t>Errore della media</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -227,47 +244,47 @@
   </fills>
   <borders count="42">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -277,7 +294,7 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -292,7 +309,7 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -304,50 +321,50 @@
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -356,27 +373,27 @@
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -385,124 +402,124 @@
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -517,10 +534,10 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -530,23 +547,23 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color theme="1"/>
       </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color theme="1"/>
       </right>
@@ -556,98 +573,98 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -659,8 +676,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -669,9 +686,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -680,168 +697,168 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="97">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="9" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="23" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="19" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="7" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="27" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="28" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="29" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="22" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="23" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="32" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="33" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="34" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="35" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="36" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="37" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="8" borderId="32" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="38" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="17" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="30" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="31" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="10" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="40" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="39" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="41" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="41" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -859,291 +876,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1354,31 +1088,30 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr codeName="Foglio1">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Foglio1"/>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.86328125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="15.46484375"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="13.9296875"/>
-    <col bestFit="1" customWidth="1" min="4" max="5" width="11.53125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14.9296875"/>
-    <col bestFit="1" customWidth="1" min="7" max="8" width="16.06640625"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="19.265625"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="11.46484375"/>
-    <col bestFit="1" customWidth="1" min="11" max="12" width="18.3984375"/>
-    <col bestFit="1" customWidth="1" min="13" max="13" width="13.1328125"/>
-    <col bestFit="1" customWidth="1" min="14" max="14" width="9.265625"/>
+    <col min="1" max="1" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="16.06640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.46484375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1405,7 +1138,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
@@ -1430,10 +1163,10 @@
         <v>0.18593999999999999</v>
       </c>
       <c r="I2" s="11">
-        <v>5.0000000000000001e-004</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
@@ -1449,7 +1182,7 @@
       </c>
       <c r="H3" s="15"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
@@ -1466,145 +1199,141 @@
       <c r="G4" s="19"/>
       <c r="H4" s="20"/>
     </row>
-    <row r="7" ht="14.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="F7" s="14"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O15" s="14"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
       <c r="Q16" s="14"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr codeName="Foglio2">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Foglio2"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="11.53125"/>
-    <col customWidth="1" min="3" max="3" width="12"/>
-    <col customWidth="1" min="4" max="4" width="12.73046875"/>
-    <col customWidth="1" min="5" max="5" width="13.53125"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12.73046875" customWidth="1"/>
+    <col min="5" max="5" width="13.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="21"/>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="74"/>
+      <c r="D1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="25"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27" t="s">
+      <c r="E1" s="76"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="31">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="27">
         <v>1</v>
       </c>
       <c r="B3" s="8">
         <v>0.249</v>
       </c>
-      <c r="C3" s="32">
-        <v>4.0000000000000001e-002</v>
-      </c>
-      <c r="D3" s="33">
+      <c r="C3" s="28">
+        <v>0.04</v>
+      </c>
+      <c r="D3" s="29">
         <v>0.76900000000000002</v>
       </c>
-      <c r="E3" s="34">
-        <v>4.2999999999999997e-002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35">
+      <c r="E3" s="30">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="32">
         <v>0.253</v>
       </c>
-      <c r="C4" s="37">
-        <v>4.2999999999999997e-002</v>
-      </c>
-      <c r="D4" s="38">
+      <c r="C4" s="33">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="D4" s="34">
         <v>0.755</v>
       </c>
       <c r="E4" s="15">
-        <v>3.7999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="32">
         <v>0.247</v>
       </c>
-      <c r="C5" s="39">
-        <v>4.2000000000000003e-002</v>
-      </c>
-      <c r="D5" s="38">
+      <c r="C5" s="35">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D5" s="34">
         <v>0.749</v>
       </c>
       <c r="E5" s="15">
-        <v>3.7999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="s">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="77">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.24959417617111146</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="43">
+      <c r="C6" s="78"/>
+      <c r="D6" s="79">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.75677401789187093</v>
       </c>
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="45" t="s">
+      <c r="E6" s="80"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="81">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
-        <v>2.4023430034058289e-002</v>
-      </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48">
+        <v>2.4023430034058289E-2</v>
+      </c>
+      <c r="C7" s="82"/>
+      <c r="D7" s="83">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
-        <v>2.2786940380104245e-002</v>
-      </c>
-      <c r="E7" s="49"/>
+        <v>2.2786940380104245E-2</v>
+      </c>
+      <c r="E7" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1615,137 +1344,133 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr codeName="Foglio3">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Foglio3"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="21"/>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="53" t="s">
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="39" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="26"/>
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="22"/>
+      <c r="B2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="58">
+      <c r="F2" s="43">
         <v>10</v>
       </c>
-      <c r="G2" s="59">
+      <c r="G2" s="44">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="31">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="27">
         <v>1</v>
       </c>
       <c r="B3">
         <v>0.26400000000000001</v>
       </c>
       <c r="C3">
-        <v>2.e-003</v>
+        <v>2E-3</v>
       </c>
       <c r="D3">
         <v>0.17599999999999999</v>
       </c>
-      <c r="E3" s="60">
-        <v>2.e-003</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35">
+      <c r="E3" s="45">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
       <c r="B4">
         <v>0.25700000000000001</v>
       </c>
       <c r="C4">
-        <v>2.e-003</v>
-      </c>
-      <c r="D4" s="61">
+        <v>2E-3</v>
+      </c>
+      <c r="D4" s="46">
         <v>0.16</v>
       </c>
-      <c r="E4" s="60">
-        <v>3.0000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="35">
+      <c r="E4" s="45">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="61">
-        <v>0.26000000000000001</v>
+      <c r="B5" s="46">
+        <v>0.26</v>
       </c>
       <c r="C5">
-        <v>3.0000000000000001e-003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D5">
         <v>0.17499999999999999</v>
       </c>
-      <c r="E5" s="62">
-        <v>2.3e-003</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="40" t="s">
+      <c r="E5" s="47">
+        <v>2.3E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="77">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.26040909090909087</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="43">
+      <c r="C6" s="78"/>
+      <c r="D6" s="79">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.17242493080080176</v>
       </c>
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="40" t="s">
+      <c r="E6" s="80"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="77">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
-        <v>1.2792042981336627e-003</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43">
+        <v>1.2792042981336627E-3</v>
+      </c>
+      <c r="C7" s="78"/>
+      <c r="D7" s="79">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
-        <v>1.3482195315735518e-003</v>
-      </c>
-      <c r="E7" s="44"/>
+        <v>1.3482195315735518E-3</v>
+      </c>
+      <c r="E7" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1755,225 +1480,220 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:E7"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr codeName="Foglio4">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Foglio4"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="7.3984375"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="9.54296875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="9.125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22.953125"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="17.79296875"/>
-    <col customWidth="1" min="6" max="6" width="15.06640625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="16.33203125"/>
-    <col customWidth="1" min="8" max="8" width="16"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="17"/>
-    <col bestFit="1" customWidth="1" min="11" max="11" width="17"/>
+    <col min="1" max="1" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.06640625" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5">
-      <c r="B1" s="63" t="s">
+    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B1" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="63" t="s">
+      <c r="G1" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="50" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="63" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="48" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="14">
         <v>0.27538000000000001</v>
       </c>
-      <c r="C2" s="66">
+      <c r="C2" s="51">
         <v>-0.26100000000000001</v>
       </c>
-      <c r="D2" s="66">
-        <v>2.e-002</v>
-      </c>
-      <c r="E2" s="66">
+      <c r="D2" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="51">
         <v>0.55800000000000005</v>
       </c>
-      <c r="F2" s="66">
-        <v>8.0000000000000002e-003</v>
-      </c>
-      <c r="G2" s="66">
+      <c r="F2" s="51">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G2" s="51">
         <v>-0.54100000000000004</v>
       </c>
-      <c r="H2" s="67">
-        <v>7.0000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="3" ht="14.65">
-      <c r="A3" s="63" t="s">
+      <c r="H2" s="52">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="53">
         <v>0.25686999999999999</v>
       </c>
-      <c r="C3" s="69">
+      <c r="C3" s="54">
         <v>-0.28599999999999998</v>
       </c>
-      <c r="D3" s="69">
+      <c r="D3" s="54">
         <f>0.04</f>
-        <v>4.0000000000000001e-002</v>
-      </c>
-      <c r="E3" s="70">
-        <v>0.64000000000000001</v>
-      </c>
-      <c r="F3" s="69">
-        <v>7.0000000000000001e-003</v>
-      </c>
-      <c r="G3" s="69">
+        <v>0.04</v>
+      </c>
+      <c r="E3" s="55">
+        <v>0.64</v>
+      </c>
+      <c r="F3" s="54">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G3" s="54">
         <v>-0.624</v>
       </c>
-      <c r="H3" s="71">
-        <v>6.0000000000000001e-003</v>
+      <c r="H3" s="56">
+        <v>6.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="14"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="17.796875"/>
-    <col customWidth="1" min="4" max="4" width="11"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="16.53125"/>
-    <col customWidth="1" min="6" max="6" width="10"/>
-    <col bestFit="1" customWidth="1" min="7" max="8" width="17.796875"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="16.53125"/>
-    <col customWidth="1" min="10" max="10" width="11.86328125"/>
-    <col bestFit="1" customWidth="1" min="11" max="11" width="13.265625"/>
-    <col bestFit="1" min="13" max="13" width="9.59765625"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="16.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="8" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.53125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.86328125" customWidth="1"/>
+    <col min="11" max="11" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.59765625" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="72" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B1" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74" t="s">
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-    </row>
-    <row r="2">
-      <c r="B2" s="75" t="s">
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B2" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="63" t="s">
+      <c r="G2" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="76" t="s">
+      <c r="J2" s="58" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="78" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="60">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C3" s="80">
+      <c r="C3" s="61">
         <v>0.51800000000000002</v>
       </c>
-      <c r="D3" s="80">
-        <v>2.8000000000000001e-002</v>
-      </c>
-      <c r="E3" s="80">
-        <v>-1.9e-002</v>
-      </c>
-      <c r="F3" s="34">
-        <v>8.0000000000000002e-003</v>
+      <c r="D3" s="61">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E3" s="61">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="F3" s="30">
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G3" s="9">
         <v>0.27538000000000001</v>
       </c>
-      <c r="H3" s="80">
+      <c r="H3" s="61">
         <v>0</v>
       </c>
-      <c r="I3" s="80">
+      <c r="I3" s="61">
         <v>0.49099999999999999</v>
       </c>
-      <c r="J3" s="34">
-        <v>1.e-002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="81"/>
+      <c r="J3" s="30">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="92"/>
       <c r="B4" s="13">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="46">
         <v>0.50900000000000001</v>
       </c>
       <c r="D4">
-        <v>1.6e-002</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E4">
         <v>-0.21299999999999999</v>
       </c>
       <c r="F4" s="15">
-        <v>1.2999999999999999e-002</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G4" s="14">
         <v>0.78227999999999998</v>
@@ -1981,15 +1701,15 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="61">
-        <v>0.23999999999999999</v>
+      <c r="I4" s="46">
+        <v>0.24</v>
       </c>
       <c r="J4" s="15">
-        <v>4.0000000000000001e-003</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="82"/>
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="93"/>
       <c r="B5" s="17">
         <v>0.76324000000000003</v>
       </c>
@@ -1997,13 +1717,13 @@
         <v>0.34599999999999997</v>
       </c>
       <c r="D5" s="19">
-        <v>1.2999999999999999e-002</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="E5" s="19">
         <v>0.16300000000000001</v>
       </c>
-      <c r="F5" s="83">
-        <v>1.e-002</v>
+      <c r="F5" s="62">
+        <v>0.01</v>
       </c>
       <c r="G5" s="18">
         <v>0.27538000000000001</v>
@@ -2015,43 +1735,43 @@
         <v>0.48499999999999999</v>
       </c>
       <c r="J5" s="20">
-        <v>1.4e-002</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="78" t="s">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="60">
         <v>0.25634000000000001</v>
       </c>
-      <c r="C6" s="80">
+      <c r="C6" s="61">
         <v>0.56899999999999995</v>
       </c>
-      <c r="D6" s="80">
-        <v>1.4e-002</v>
-      </c>
-      <c r="E6" s="80">
+      <c r="D6" s="61">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E6" s="61">
         <v>0.251</v>
       </c>
-      <c r="F6" s="34">
-        <v>2.4e-002</v>
-      </c>
-      <c r="G6" s="80">
+      <c r="F6" s="30">
+        <v>2.4E-2</v>
+      </c>
+      <c r="G6" s="61">
         <v>0.27538000000000001</v>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="61">
         <v>0</v>
       </c>
-      <c r="I6" s="80">
+      <c r="I6" s="61">
         <v>0.251</v>
       </c>
-      <c r="J6" s="34">
-        <v>2.4e-002</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="81"/>
+      <c r="J6" s="30">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="92"/>
       <c r="B7" s="13">
         <v>0.25634000000000001</v>
       </c>
@@ -2059,13 +1779,13 @@
         <v>0.56899999999999995</v>
       </c>
       <c r="D7">
-        <v>4.0000000000000001e-003</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E7">
         <v>0.13200000000000001</v>
       </c>
       <c r="F7" s="15">
-        <v>1.2e-002</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G7" s="14">
         <v>0.78227999999999998</v>
@@ -2077,25 +1797,25 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="J7" s="15">
-        <v>1.2e-002</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="82"/>
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="93"/>
       <c r="B8" s="17">
         <v>0.76324000000000003</v>
       </c>
       <c r="C8" s="19">
-        <v>0.47999999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="D8" s="19">
-        <v>4.0000000000000001e-003</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E8" s="19">
         <v>0.34399999999999997</v>
       </c>
       <c r="F8" s="20">
-        <v>1.4999999999999999e-002</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G8" s="18">
         <v>0.27538000000000001</v>
@@ -2107,11 +1827,11 @@
         <v>0.34399999999999997</v>
       </c>
       <c r="J8" s="20">
-        <v>1.4999999999999999e-002</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="84"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2120,54 +1840,53 @@
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="87" t="s">
+      <c r="B1" s="95"/>
+      <c r="C1" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="86"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="75" t="s">
+      <c r="D1" s="95"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="59" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="88">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="64">
         <v>0.29006999999999999</v>
       </c>
-      <c r="B3" s="89">
+      <c r="B3" s="65">
         <v>0.68100000000000005</v>
       </c>
-      <c r="C3" s="90">
+      <c r="C3" s="66">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
-      <c r="D3" s="89">
-        <v>0.93600000000000005</v>
+      <c r="D3" s="65">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -2175,78 +1894,72 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr codeName="Foglio5">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Foglio5"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.46484375"/>
-    <col bestFit="1" customWidth="1" min="2" max="3" width="16.9296875"/>
+    <col min="1" max="1" width="18.46484375" customWidth="1"/>
+    <col min="2" max="3" width="16.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="91" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B1" s="67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="92">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B2" s="68">
         <v>1.478</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="92">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B3" s="68">
         <v>1.5192000000000001</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="92">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B4" s="68">
         <v>1.5113000000000001</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="92">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B5" s="68">
         <v>1.5176000000000001</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="92">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B6" s="68">
         <v>1.5246999999999999</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="93" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="94">
+      <c r="B7" s="70">
         <f>AVERAGE(B2:B6)</f>
         <v>1.5101600000000002</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="95" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="96">
+      <c r="B8" s="72">
         <f>_xlfn.STDEV.S(B2:B6)/SQRT(COUNT(B2:B6))</f>
-        <v>8.3188100110532705e-003</v>
+        <v>8.3188100110532705E-3</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -2254,7 +1967,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="EB146277-E2E3-4D76-8D30-7199B5C8E298">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DFC530-79CE-411B-9AC4-7A4DC899DC0E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Urti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A17223F8177C2D7C57AFC4E2DF361A09DF181B28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA26FCAD-1D36-4FE8-8DBD-3EA9885CC08C}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_A17223F8177C2D7C57AFC4E2DF361A09DF181B28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79FF0517-3DFD-4E19-880F-9863DF6286A5}"/>
   <bookViews>
     <workbookView xWindow="1688" yWindow="2670" windowWidth="16200" windowHeight="9307" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -787,6 +787,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -849,15 +858,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1230,14 +1230,14 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="21"/>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75" t="s">
+      <c r="C1" s="77"/>
+      <c r="D1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="76"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="22"/>
@@ -1309,31 +1309,31 @@
       <c r="A6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="80">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.24959417617111146</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="79">
+      <c r="C6" s="81"/>
+      <c r="D6" s="82">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.75677401789187093</v>
       </c>
-      <c r="E6" s="80"/>
+      <c r="E6" s="83"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="84">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
         <v>2.4023430034058289E-2</v>
       </c>
-      <c r="C7" s="82"/>
-      <c r="D7" s="83">
+      <c r="C7" s="85"/>
+      <c r="D7" s="86">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
         <v>2.2786940380104245E-2</v>
       </c>
-      <c r="E7" s="84"/>
+      <c r="E7" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1357,12 +1357,12 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="21"/>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="90"/>
       <c r="F1" s="38" t="s">
         <v>18</v>
       </c>
@@ -1446,31 +1446,31 @@
       <c r="A6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="80">
         <f>((B3/(C3)^2)+(B4/(C4)^2)+(B5/(C5)^2))/((1/C3^2)+(1/C4^2)+(1/C5^2))</f>
         <v>0.26040909090909087</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="79">
+      <c r="C6" s="81"/>
+      <c r="D6" s="82">
         <f>((D3/(E3)^2)+(D4/(E4)^2)+(D5/(E5)^2))/((1/E3^2)+(1/E4^2)+(1/E5^2))</f>
         <v>0.17242493080080176</v>
       </c>
-      <c r="E6" s="80"/>
+      <c r="E6" s="83"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="77">
+      <c r="B7" s="80">
         <f>SQRT(1/((1/C3^2)+(1/C4^2)+(1/C5^2)))</f>
         <v>1.2792042981336627E-3</v>
       </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="79">
+      <c r="C7" s="81"/>
+      <c r="D7" s="82">
         <f>SQRT(1/((1/E3^2)+(1/E4^2)+(1/E5^2)))</f>
         <v>1.3482195315735518E-3</v>
       </c>
-      <c r="E7" s="80"/>
+      <c r="E7" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1603,19 +1603,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="90" t="s">
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B2" s="57" t="s">
@@ -1647,7 +1647,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="91" t="s">
+      <c r="A3" s="94" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="60">
@@ -1679,7 +1679,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="92"/>
+      <c r="A4" s="95"/>
       <c r="B4" s="13">
         <v>0.25634000000000001</v>
       </c>
@@ -1709,7 +1709,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="93"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="17">
         <v>0.76324000000000003</v>
       </c>
@@ -1739,7 +1739,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="94" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="60">
@@ -1771,7 +1771,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="92"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="13">
         <v>0.25634000000000001</v>
       </c>
@@ -1801,7 +1801,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="93"/>
+      <c r="A8" s="96"/>
       <c r="B8" s="17">
         <v>0.76324000000000003</v>
       </c>
@@ -1851,14 +1851,14 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="96" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="95"/>
+      <c r="D1" s="74"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="57" t="s">
@@ -1879,7 +1879,7 @@
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="65">
-        <v>0.68100000000000005</v>
+        <v>0.64</v>
       </c>
       <c r="C3" s="66">
         <f>0.29007+0.18594</f>

--- a/Urti/Urti.xlsx
+++ b/Urti/Urti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/Urti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_A17223F8177C2D7C57AFC4E2DF361A09DF181B28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79FF0517-3DFD-4E19-880F-9863DF6286A5}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_A17223F8177C2D7C57AFC4E2DF361A09DF181B28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC00FAD2-D013-4B83-9A5F-CE93CDAC759B}"/>
   <bookViews>
     <workbookView xWindow="1688" yWindow="2670" windowWidth="16200" windowHeight="9307" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1879,14 +1879,14 @@
         <v>0.29006999999999999</v>
       </c>
       <c r="B3" s="65">
-        <v>0.64</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="C3" s="66">
         <f>0.29007+0.18594</f>
         <v>0.47600999999999999</v>
       </c>
       <c r="D3" s="65">
-        <v>0.87</v>
+        <v>0.93600000000000005</v>
       </c>
     </row>
   </sheetData>
